--- a/research/traditional_assets/database/data/new_zealand/new_zealand_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_healthcare_support_services.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0814806265346875</v>
+        <v>0.08128488078039038</v>
       </c>
       <c r="C2">
-        <v>15.69890348046517</v>
+        <v>15.56680289545264</v>
       </c>
       <c r="D2">
-        <v>14.63890348046517</v>
+        <v>14.66690289545264</v>
       </c>
       <c r="E2">
-        <v>-2.41</v>
+        <v>-2.2499</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1601</v>
       </c>
       <c r="G2">
         <v>1.06</v>
@@ -1564,28 +1564,28 @@
         <v>2.006</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008053029999999999</v>
       </c>
       <c r="N2">
-        <v>2.006</v>
+        <v>1.99794697</v>
       </c>
       <c r="O2">
-        <v>0.5616800000000001</v>
+        <v>0.5594251516000002</v>
       </c>
       <c r="P2">
-        <v>1.44432</v>
+        <v>1.4385218184</v>
       </c>
       <c r="Q2">
-        <v>1.92832</v>
+        <v>1.9225218184</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0814806265346875</v>
+        <v>0.08174012200039432</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738455</v>
+        <v>0.8300259122492917</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>249.0987864195217</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08128488078039038</v>
+        <v>0.08108913502609326</v>
       </c>
       <c r="C3">
-        <v>15.56680289545264</v>
+        <v>15.43480962306583</v>
       </c>
       <c r="D3">
-        <v>14.66690289545264</v>
+        <v>14.69500962306583</v>
       </c>
       <c r="E3">
-        <v>-2.2499</v>
+        <v>-2.0898</v>
       </c>
       <c r="F3">
-        <v>0.1601</v>
+        <v>0.3202</v>
       </c>
       <c r="G3">
         <v>1.06</v>
@@ -1646,28 +1646,28 @@
         <v>2.006</v>
       </c>
       <c r="M3">
-        <v>0.008053029999999999</v>
+        <v>0.01610606</v>
       </c>
       <c r="N3">
-        <v>1.99794697</v>
+        <v>1.98989394</v>
       </c>
       <c r="O3">
-        <v>0.5594251516000002</v>
+        <v>0.5571703032000002</v>
       </c>
       <c r="P3">
-        <v>1.4385218184</v>
+        <v>1.4327236368</v>
       </c>
       <c r="Q3">
-        <v>1.9225218184</v>
+        <v>1.9167236368</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08174012200039432</v>
+        <v>0.08200491329193189</v>
       </c>
       <c r="T3">
-        <v>0.8300259122492917</v>
+        <v>0.8361411845711755</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>249.0987864195217</v>
+        <v>124.5493932097608</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08108913502609326</v>
+        <v>0.08089338927179612</v>
       </c>
       <c r="C4">
-        <v>15.43480962306583</v>
+        <v>15.3029242814307</v>
       </c>
       <c r="D4">
-        <v>14.69500962306583</v>
+        <v>14.7232242814307</v>
       </c>
       <c r="E4">
-        <v>-2.0898</v>
+        <v>-1.9297</v>
       </c>
       <c r="F4">
-        <v>0.3202</v>
+        <v>0.4802999999999999</v>
       </c>
       <c r="G4">
         <v>1.06</v>
@@ -1728,28 +1728,28 @@
         <v>2.006</v>
       </c>
       <c r="M4">
-        <v>0.01610606</v>
+        <v>0.02415909</v>
       </c>
       <c r="N4">
-        <v>1.98989394</v>
+        <v>1.98184091</v>
       </c>
       <c r="O4">
-        <v>0.5571703032000002</v>
+        <v>0.5549154548000002</v>
       </c>
       <c r="P4">
-        <v>1.4327236368</v>
+        <v>1.4269254552</v>
       </c>
       <c r="Q4">
-        <v>1.9167236368</v>
+        <v>1.9109254552</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08200491329193189</v>
+        <v>0.08227516419772797</v>
       </c>
       <c r="T4">
-        <v>0.8361411845711755</v>
+        <v>0.8423825449821704</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>124.5493932097608</v>
+        <v>83.03292880650721</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08089338927179612</v>
+        <v>0.080697643517499</v>
       </c>
       <c r="C5">
-        <v>15.3029242814307</v>
+        <v>15.17114749342962</v>
       </c>
       <c r="D5">
-        <v>14.7232242814307</v>
+        <v>14.75154749342962</v>
       </c>
       <c r="E5">
-        <v>-1.9297</v>
+        <v>-1.7696</v>
       </c>
       <c r="F5">
-        <v>0.4802999999999999</v>
+        <v>0.6404</v>
       </c>
       <c r="G5">
         <v>1.06</v>
@@ -1810,28 +1810,28 @@
         <v>2.006</v>
       </c>
       <c r="M5">
-        <v>0.02415909</v>
+        <v>0.03221212</v>
       </c>
       <c r="N5">
-        <v>1.98184091</v>
+        <v>1.97378788</v>
       </c>
       <c r="O5">
-        <v>0.5549154548000002</v>
+        <v>0.5526606064000001</v>
       </c>
       <c r="P5">
-        <v>1.4269254552</v>
+        <v>1.4211272736</v>
       </c>
       <c r="Q5">
-        <v>1.9109254552</v>
+        <v>1.9051272736</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08227516419772797</v>
+        <v>0.08255104533072813</v>
       </c>
       <c r="T5">
-        <v>0.8423825449821704</v>
+        <v>0.8487539337350609</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>83.03292880650721</v>
+        <v>62.27469660488041</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.080697643517499</v>
+        <v>0.08050189776320187</v>
       </c>
       <c r="C6">
-        <v>15.17114749342962</v>
+        <v>15.03947988674717</v>
       </c>
       <c r="D6">
-        <v>14.75154749342962</v>
+        <v>14.77997988674717</v>
       </c>
       <c r="E6">
-        <v>-1.7696</v>
+        <v>-1.6095</v>
       </c>
       <c r="F6">
-        <v>0.6404</v>
+        <v>0.8005</v>
       </c>
       <c r="G6">
         <v>1.06</v>
@@ -1892,28 +1892,28 @@
         <v>2.006</v>
       </c>
       <c r="M6">
-        <v>0.03221212</v>
+        <v>0.04026515</v>
       </c>
       <c r="N6">
-        <v>1.97378788</v>
+        <v>1.96573485</v>
       </c>
       <c r="O6">
-        <v>0.5526606064000001</v>
+        <v>0.5504057580000001</v>
       </c>
       <c r="P6">
-        <v>1.4211272736</v>
+        <v>1.415329092</v>
       </c>
       <c r="Q6">
-        <v>1.9051272736</v>
+        <v>1.899329092</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08255104533072813</v>
+        <v>0.08283273448758091</v>
       </c>
       <c r="T6">
-        <v>0.8487539337350609</v>
+        <v>0.8552594569880122</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>62.27469660488041</v>
+        <v>49.81975728390432</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08050189776320187</v>
+        <v>0.08030615200890476</v>
       </c>
       <c r="C7">
-        <v>15.03947988674717</v>
+        <v>14.90792209391651</v>
       </c>
       <c r="D7">
-        <v>14.77997988674717</v>
+        <v>14.80852209391651</v>
       </c>
       <c r="E7">
-        <v>-1.6095</v>
+        <v>-1.4494</v>
       </c>
       <c r="F7">
-        <v>0.8005</v>
+        <v>0.9606</v>
       </c>
       <c r="G7">
         <v>1.06</v>
@@ -1974,28 +1974,28 @@
         <v>2.006</v>
       </c>
       <c r="M7">
-        <v>0.04026515</v>
+        <v>0.04831818</v>
       </c>
       <c r="N7">
-        <v>1.96573485</v>
+        <v>1.95768182</v>
       </c>
       <c r="O7">
-        <v>0.5504057580000001</v>
+        <v>0.5481509096000001</v>
       </c>
       <c r="P7">
-        <v>1.415329092</v>
+        <v>1.4095309104</v>
       </c>
       <c r="Q7">
-        <v>1.899329092</v>
+        <v>1.8935309104</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08283273448758091</v>
+        <v>0.08312041703074974</v>
       </c>
       <c r="T7">
-        <v>0.8552594569880122</v>
+        <v>0.8619033956293244</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.81975728390432</v>
+        <v>41.51646440325361</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08030615200890476</v>
+        <v>0.08011040625460765</v>
       </c>
       <c r="C8">
-        <v>14.90792209391651</v>
+        <v>14.7764747523663</v>
       </c>
       <c r="D8">
-        <v>14.80852209391651</v>
+        <v>14.8371747523663</v>
       </c>
       <c r="E8">
-        <v>-1.4494</v>
+        <v>-1.2893</v>
       </c>
       <c r="F8">
-        <v>0.9605999999999999</v>
+        <v>1.1207</v>
       </c>
       <c r="G8">
         <v>1.06</v>
@@ -2056,28 +2056,28 @@
         <v>2.006</v>
       </c>
       <c r="M8">
-        <v>0.04831818</v>
+        <v>0.05637120999999998</v>
       </c>
       <c r="N8">
-        <v>1.95768182</v>
+        <v>1.94962879</v>
       </c>
       <c r="O8">
-        <v>0.5481509096000001</v>
+        <v>0.5458960612000001</v>
       </c>
       <c r="P8">
-        <v>1.4095309104</v>
+        <v>1.4037327288</v>
       </c>
       <c r="Q8">
-        <v>1.8935309104</v>
+        <v>1.8877327288</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08312041703074974</v>
+        <v>0.08341428629527703</v>
       </c>
       <c r="T8">
-        <v>0.8619033956293244</v>
+        <v>0.8686902146715249</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.51646440325361</v>
+        <v>35.58554091707452</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08011040625460764</v>
+        <v>0.07991466050031051</v>
       </c>
       <c r="C9">
-        <v>14.7764747523663</v>
+        <v>14.64513850446815</v>
       </c>
       <c r="D9">
-        <v>14.8371747523663</v>
+        <v>14.86593850446815</v>
       </c>
       <c r="E9">
-        <v>-1.2893</v>
+        <v>-1.1292</v>
       </c>
       <c r="F9">
-        <v>1.1207</v>
+        <v>1.2808</v>
       </c>
       <c r="G9">
         <v>1.06</v>
@@ -2138,28 +2138,28 @@
         <v>2.006</v>
       </c>
       <c r="M9">
-        <v>0.05637121</v>
+        <v>0.06442423999999999</v>
       </c>
       <c r="N9">
-        <v>1.94962879</v>
+        <v>1.94157576</v>
       </c>
       <c r="O9">
-        <v>0.5458960612000001</v>
+        <v>0.5436412128000001</v>
       </c>
       <c r="P9">
-        <v>1.4037327288</v>
+        <v>1.3979345472</v>
       </c>
       <c r="Q9">
-        <v>1.8877327288</v>
+        <v>1.8819345472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08341428629527703</v>
+        <v>0.08371454402207663</v>
       </c>
       <c r="T9">
-        <v>0.8686902146715249</v>
+        <v>0.875624573258121</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.58554091707452</v>
+        <v>31.13734830244021</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07991466050031051</v>
+        <v>0.07971891474601338</v>
       </c>
       <c r="C10">
-        <v>14.64513850446815</v>
+        <v>14.51391399758461</v>
       </c>
       <c r="D10">
-        <v>14.86593850446815</v>
+        <v>14.89481399758461</v>
       </c>
       <c r="E10">
-        <v>-1.1292</v>
+        <v>-0.9691000000000003</v>
       </c>
       <c r="F10">
-        <v>1.2808</v>
+        <v>1.4409</v>
       </c>
       <c r="G10">
         <v>1.06</v>
@@ -2220,28 +2220,28 @@
         <v>2.006</v>
       </c>
       <c r="M10">
-        <v>0.06442423999999999</v>
+        <v>0.07247726999999998</v>
       </c>
       <c r="N10">
-        <v>1.94157576</v>
+        <v>1.93352273</v>
       </c>
       <c r="O10">
-        <v>0.5436412128000001</v>
+        <v>0.5413863644000001</v>
       </c>
       <c r="P10">
-        <v>1.3979345472</v>
+        <v>1.3921363656</v>
       </c>
       <c r="Q10">
-        <v>1.8819345472</v>
+        <v>1.8761363656</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08371454402207663</v>
+        <v>0.08402140081979492</v>
       </c>
       <c r="T10">
-        <v>0.875624573258121</v>
+        <v>0.882711335330137</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.13734830244021</v>
+        <v>27.67764293550241</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07971891474601338</v>
+        <v>0.07952316899171627</v>
       </c>
       <c r="C11">
-        <v>14.51391399758461</v>
+        <v>14.38280188411776</v>
       </c>
       <c r="D11">
-        <v>14.89481399758461</v>
+        <v>14.92380188411776</v>
       </c>
       <c r="E11">
-        <v>-0.9691000000000003</v>
+        <v>-0.8090000000000004</v>
       </c>
       <c r="F11">
-        <v>1.4409</v>
+        <v>1.601</v>
       </c>
       <c r="G11">
         <v>1.06</v>
@@ -2302,28 +2302,28 @@
         <v>2.006</v>
       </c>
       <c r="M11">
-        <v>0.07247726999999998</v>
+        <v>0.08053029999999999</v>
       </c>
       <c r="N11">
-        <v>1.93352273</v>
+        <v>1.9254697</v>
       </c>
       <c r="O11">
-        <v>0.5413863644000001</v>
+        <v>0.5391315160000001</v>
       </c>
       <c r="P11">
-        <v>1.3921363656</v>
+        <v>1.386338184</v>
       </c>
       <c r="Q11">
-        <v>1.8761363656</v>
+        <v>1.870338184</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08402140081979492</v>
+        <v>0.08433507665746251</v>
       </c>
       <c r="T11">
-        <v>0.882711335330137</v>
+        <v>0.8899555810037533</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.67764293550241</v>
+        <v>24.90987864195217</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07952316899171627</v>
+        <v>0.07932742323741915</v>
       </c>
       <c r="C12">
-        <v>14.38280188411776</v>
+        <v>14.25180282155832</v>
       </c>
       <c r="D12">
-        <v>14.92380188411776</v>
+        <v>14.95290282155832</v>
       </c>
       <c r="E12">
-        <v>-0.8090000000000002</v>
+        <v>-0.6489000000000003</v>
       </c>
       <c r="F12">
-        <v>1.601</v>
+        <v>1.7611</v>
       </c>
       <c r="G12">
         <v>1.06</v>
@@ -2384,28 +2384,28 @@
         <v>2.006</v>
       </c>
       <c r="M12">
-        <v>0.0805303</v>
+        <v>0.08858332999999999</v>
       </c>
       <c r="N12">
-        <v>1.9254697</v>
+        <v>1.91741667</v>
       </c>
       <c r="O12">
-        <v>0.5391315160000001</v>
+        <v>0.5368766676000001</v>
       </c>
       <c r="P12">
-        <v>1.386338184</v>
+        <v>1.3805400024</v>
       </c>
       <c r="Q12">
-        <v>1.870338184</v>
+        <v>1.8645400024</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08433507665746251</v>
+        <v>0.08465580139035858</v>
       </c>
       <c r="T12">
-        <v>0.8899555810037533</v>
+        <v>0.8973626187149788</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.90987864195217</v>
+        <v>22.64534421995651</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07932742323741915</v>
+        <v>0.07913167748312201</v>
       </c>
       <c r="C13">
-        <v>14.25180282155832</v>
+        <v>14.12091747253539</v>
       </c>
       <c r="D13">
-        <v>14.95290282155832</v>
+        <v>14.98211747253539</v>
       </c>
       <c r="E13">
-        <v>-0.6489000000000003</v>
+        <v>-0.4888000000000003</v>
       </c>
       <c r="F13">
-        <v>1.7611</v>
+        <v>1.9212</v>
       </c>
       <c r="G13">
         <v>1.06</v>
@@ -2466,28 +2466,28 @@
         <v>2.006</v>
       </c>
       <c r="M13">
-        <v>0.08858332999999999</v>
+        <v>0.09663635999999999</v>
       </c>
       <c r="N13">
-        <v>1.91741667</v>
+        <v>1.90936364</v>
       </c>
       <c r="O13">
-        <v>0.5368766676000001</v>
+        <v>0.5346218192000001</v>
       </c>
       <c r="P13">
-        <v>1.3805400024</v>
+        <v>1.3747418208</v>
       </c>
       <c r="Q13">
-        <v>1.8645400024</v>
+        <v>1.8587418208</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08465580139035858</v>
+        <v>0.08498381532172955</v>
       </c>
       <c r="T13">
-        <v>0.8973626187149788</v>
+        <v>0.9049379981923685</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.64534421995651</v>
+        <v>20.7582322016268</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07913167748312201</v>
+        <v>0.07893593172882488</v>
       </c>
       <c r="C14">
-        <v>14.12091747253539</v>
+        <v>13.99014650486671</v>
       </c>
       <c r="D14">
-        <v>14.98211747253539</v>
+        <v>15.01144650486671</v>
       </c>
       <c r="E14">
-        <v>-0.4888000000000003</v>
+        <v>-0.3287000000000004</v>
       </c>
       <c r="F14">
-        <v>1.9212</v>
+        <v>2.0813</v>
       </c>
       <c r="G14">
         <v>1.06</v>
@@ -2548,28 +2548,28 @@
         <v>2.006</v>
       </c>
       <c r="M14">
-        <v>0.09663635999999999</v>
+        <v>0.10468939</v>
       </c>
       <c r="N14">
-        <v>1.90936364</v>
+        <v>1.90131061</v>
       </c>
       <c r="O14">
-        <v>0.5346218192000001</v>
+        <v>0.5323669708000002</v>
       </c>
       <c r="P14">
-        <v>1.3747418208</v>
+        <v>1.3689436392</v>
       </c>
       <c r="Q14">
-        <v>1.8587418208</v>
+        <v>1.8529436392</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08498381532172955</v>
+        <v>0.08531936980324697</v>
       </c>
       <c r="T14">
-        <v>0.9049379981923685</v>
+        <v>0.9126875243244109</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.7582322016268</v>
+        <v>19.16144510919398</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07893593172882488</v>
+        <v>0.07874018597452775</v>
       </c>
       <c r="C15">
-        <v>13.99014650486671</v>
+        <v>13.85949059160957</v>
       </c>
       <c r="D15">
-        <v>15.01144650486671</v>
+        <v>15.04089059160957</v>
       </c>
       <c r="E15">
-        <v>-0.3287000000000004</v>
+        <v>-0.1686000000000001</v>
       </c>
       <c r="F15">
-        <v>2.0813</v>
+        <v>2.2414</v>
       </c>
       <c r="G15">
         <v>1.06</v>
@@ -2630,28 +2630,28 @@
         <v>2.006</v>
       </c>
       <c r="M15">
-        <v>0.10468939</v>
+        <v>0.11274242</v>
       </c>
       <c r="N15">
-        <v>1.90131061</v>
+        <v>1.89325758</v>
       </c>
       <c r="O15">
-        <v>0.5323669708000002</v>
+        <v>0.5301121224000002</v>
       </c>
       <c r="P15">
-        <v>1.3689436392</v>
+        <v>1.3631454576</v>
       </c>
       <c r="Q15">
-        <v>1.8529436392</v>
+        <v>1.8471454576</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08531936980324697</v>
+        <v>0.08566272787735785</v>
       </c>
       <c r="T15">
-        <v>0.9126875243244109</v>
+        <v>0.9206172719944079</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.16144510919398</v>
+        <v>17.79277045853726</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07874018597452775</v>
+        <v>0.07854444022023063</v>
       </c>
       <c r="C16">
-        <v>13.85949059160957</v>
+        <v>13.72895041111231</v>
       </c>
       <c r="D16">
-        <v>15.04089059160957</v>
+        <v>15.07045041111231</v>
       </c>
       <c r="E16">
-        <v>-0.1686000000000001</v>
+        <v>-0.008500000000000174</v>
       </c>
       <c r="F16">
-        <v>2.2414</v>
+        <v>2.4015</v>
       </c>
       <c r="G16">
         <v>1.06</v>
@@ -2712,28 +2712,28 @@
         <v>2.006</v>
       </c>
       <c r="M16">
-        <v>0.11274242</v>
+        <v>0.12079545</v>
       </c>
       <c r="N16">
-        <v>1.89325758</v>
+        <v>1.88520455</v>
       </c>
       <c r="O16">
-        <v>0.5301121224000002</v>
+        <v>0.5278572740000002</v>
       </c>
       <c r="P16">
-        <v>1.3631454576</v>
+        <v>1.357347276</v>
       </c>
       <c r="Q16">
-        <v>1.8471454576</v>
+        <v>1.841347276</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08566272787735785</v>
+        <v>0.08601416496497721</v>
       </c>
       <c r="T16">
-        <v>0.9206172719944079</v>
+        <v>0.9287336019625223</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.79277045853726</v>
+        <v>16.60658576130144</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07854444022023063</v>
+        <v>0.0783486944659335</v>
       </c>
       <c r="C17">
-        <v>13.72895041111232</v>
+        <v>13.59852664706637</v>
       </c>
       <c r="D17">
-        <v>15.07045041111231</v>
+        <v>15.10012664706638</v>
       </c>
       <c r="E17">
-        <v>-0.008500000000000618</v>
+        <v>0.1515999999999997</v>
       </c>
       <c r="F17">
-        <v>2.4015</v>
+        <v>2.5616</v>
       </c>
       <c r="G17">
         <v>1.06</v>
@@ -2794,28 +2794,28 @@
         <v>2.006</v>
       </c>
       <c r="M17">
-        <v>0.12079545</v>
+        <v>0.12884848</v>
       </c>
       <c r="N17">
-        <v>1.88520455</v>
+        <v>1.87715152</v>
       </c>
       <c r="O17">
-        <v>0.5278572740000002</v>
+        <v>0.5256024256000001</v>
       </c>
       <c r="P17">
-        <v>1.357347276</v>
+        <v>1.3515490944</v>
       </c>
       <c r="Q17">
-        <v>1.841347276</v>
+        <v>1.8355490944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08601416496497721</v>
+        <v>0.08637396960230179</v>
       </c>
       <c r="T17">
-        <v>0.9287336019625223</v>
+        <v>0.9370431778822587</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.60658576130145</v>
+        <v>15.5686741512201</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0783486944659335</v>
+        <v>0.07815294871163637</v>
       </c>
       <c r="C18">
-        <v>13.59852664706637</v>
+        <v>13.46821998855903</v>
       </c>
       <c r="D18">
-        <v>15.10012664706638</v>
+        <v>15.12991998855903</v>
       </c>
       <c r="E18">
-        <v>0.1515999999999997</v>
+        <v>0.3116999999999996</v>
       </c>
       <c r="F18">
-        <v>2.5616</v>
+        <v>2.7217</v>
       </c>
       <c r="G18">
         <v>1.06</v>
@@ -2876,28 +2876,28 @@
         <v>2.006</v>
       </c>
       <c r="M18">
-        <v>0.12884848</v>
+        <v>0.13690151</v>
       </c>
       <c r="N18">
-        <v>1.87715152</v>
+        <v>1.86909849</v>
       </c>
       <c r="O18">
-        <v>0.5256024256000001</v>
+        <v>0.5233475772000001</v>
       </c>
       <c r="P18">
-        <v>1.3515490944</v>
+        <v>1.3457509128</v>
       </c>
       <c r="Q18">
-        <v>1.8355490944</v>
+        <v>1.8297509128</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08637396960230179</v>
+        <v>0.0867424442308872</v>
       </c>
       <c r="T18">
-        <v>0.9370431778822587</v>
+        <v>0.9455529845470487</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.5686741512201</v>
+        <v>14.65286978938363</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07815294871163637</v>
+        <v>0.07795720295733927</v>
       </c>
       <c r="C19">
-        <v>13.46821998855903</v>
+        <v>13.33803113012676</v>
       </c>
       <c r="D19">
-        <v>15.12991998855903</v>
+        <v>15.15983113012676</v>
       </c>
       <c r="E19">
-        <v>0.3116999999999996</v>
+        <v>0.4718</v>
       </c>
       <c r="F19">
-        <v>2.7217</v>
+        <v>2.8818</v>
       </c>
       <c r="G19">
         <v>1.06</v>
@@ -2958,28 +2958,28 @@
         <v>2.006</v>
       </c>
       <c r="M19">
-        <v>0.13690151</v>
+        <v>0.14495454</v>
       </c>
       <c r="N19">
-        <v>1.86909849</v>
+        <v>1.86104546</v>
       </c>
       <c r="O19">
-        <v>0.5233475772000001</v>
+        <v>0.5210927288000001</v>
       </c>
       <c r="P19">
-        <v>1.3457509128</v>
+        <v>1.3399527312</v>
       </c>
       <c r="Q19">
-        <v>1.8297509128</v>
+        <v>1.8239527312</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0867424442308872</v>
+        <v>0.08711990604553568</v>
       </c>
       <c r="T19">
-        <v>0.9455529845470487</v>
+        <v>0.9542703474719557</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.65286978938363</v>
+        <v>13.8388214677512</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07795720295733927</v>
+        <v>0.07776145720304213</v>
       </c>
       <c r="C20">
-        <v>13.33803113012676</v>
+        <v>13.20796077180914</v>
       </c>
       <c r="D20">
-        <v>15.15983113012676</v>
+        <v>15.18986077180914</v>
       </c>
       <c r="E20">
-        <v>0.4717999999999996</v>
+        <v>0.6318999999999995</v>
       </c>
       <c r="F20">
-        <v>2.8818</v>
+        <v>3.0419</v>
       </c>
       <c r="G20">
         <v>1.06</v>
@@ -3040,28 +3040,28 @@
         <v>2.006</v>
       </c>
       <c r="M20">
-        <v>0.14495454</v>
+        <v>0.15300757</v>
       </c>
       <c r="N20">
-        <v>1.86104546</v>
+        <v>1.85299243</v>
       </c>
       <c r="O20">
-        <v>0.5210927288000001</v>
+        <v>0.5188378804000001</v>
       </c>
       <c r="P20">
-        <v>1.3399527312</v>
+        <v>1.3341545496</v>
       </c>
       <c r="Q20">
-        <v>1.8239527312</v>
+        <v>1.8181545496</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08711990604553568</v>
+        <v>0.08750668790499028</v>
       </c>
       <c r="T20">
-        <v>0.9542703474719557</v>
+        <v>0.9632029539258727</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.8388214677512</v>
+        <v>13.11046244313272</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07776145720304213</v>
+        <v>0.077781711448745</v>
       </c>
       <c r="C21">
-        <v>13.20796077180914</v>
+        <v>13.04474802141481</v>
       </c>
       <c r="D21">
-        <v>15.18986077180914</v>
+        <v>15.18674802141481</v>
       </c>
       <c r="E21">
-        <v>0.6318999999999995</v>
+        <v>0.7919999999999998</v>
       </c>
       <c r="F21">
-        <v>3.0419</v>
+        <v>3.202</v>
       </c>
       <c r="G21">
         <v>1.06</v>
@@ -3122,45 +3122,45 @@
         <v>2.006</v>
       </c>
       <c r="M21">
-        <v>0.15300757</v>
+        <v>0.1658636</v>
       </c>
       <c r="N21">
-        <v>1.85299243</v>
+        <v>1.8401364</v>
       </c>
       <c r="O21">
-        <v>0.5188378804000001</v>
+        <v>0.5152381920000001</v>
       </c>
       <c r="P21">
-        <v>1.3341545496</v>
+        <v>1.324898208</v>
       </c>
       <c r="Q21">
-        <v>1.8181545496</v>
+        <v>1.808898208</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08750668790499028</v>
+        <v>0.08790313931093124</v>
       </c>
       <c r="T21">
-        <v>0.9632029539258727</v>
+        <v>0.9723588755411376</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.28</v>
       </c>
       <c r="W21">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.11046244313272</v>
+        <v>12.09427505492465</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.077781711448745</v>
+        <v>0.07759676569444789</v>
       </c>
       <c r="C22">
-        <v>13.04474802141481</v>
+        <v>12.9131186458903</v>
       </c>
       <c r="D22">
-        <v>15.18674802141481</v>
+        <v>15.2152186458903</v>
       </c>
       <c r="E22">
-        <v>0.7919999999999998</v>
+        <v>0.9520999999999997</v>
       </c>
       <c r="F22">
-        <v>3.202</v>
+        <v>3.3621</v>
       </c>
       <c r="G22">
         <v>1.06</v>
@@ -3204,28 +3204,28 @@
         <v>2.006</v>
       </c>
       <c r="M22">
-        <v>0.1658636</v>
+        <v>0.17415678</v>
       </c>
       <c r="N22">
-        <v>1.8401364</v>
+        <v>1.83184322</v>
       </c>
       <c r="O22">
-        <v>0.5152381920000001</v>
+        <v>0.5129161016000001</v>
       </c>
       <c r="P22">
-        <v>1.324898208</v>
+        <v>1.3189271184</v>
       </c>
       <c r="Q22">
-        <v>1.808898208</v>
+        <v>1.8029271184</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08790313931093124</v>
+        <v>0.08830962746132642</v>
       </c>
       <c r="T22">
-        <v>0.9723588755411376</v>
+        <v>0.9817465926403335</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.09427505492465</v>
+        <v>11.51835719516633</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07759676569444789</v>
+        <v>0.07741181994015076</v>
       </c>
       <c r="C23">
-        <v>12.9131186458903</v>
+        <v>12.78159621872633</v>
       </c>
       <c r="D23">
-        <v>15.2152186458903</v>
+        <v>15.24379621872633</v>
       </c>
       <c r="E23">
-        <v>0.9520999999999993</v>
+        <v>1.1122</v>
       </c>
       <c r="F23">
-        <v>3.362099999999999</v>
+        <v>3.5222</v>
       </c>
       <c r="G23">
         <v>1.06</v>
@@ -3286,28 +3286,28 @@
         <v>2.006</v>
       </c>
       <c r="M23">
-        <v>0.17415678</v>
+        <v>0.18244996</v>
       </c>
       <c r="N23">
-        <v>1.83184322</v>
+        <v>1.82355004</v>
       </c>
       <c r="O23">
-        <v>0.5129161016000001</v>
+        <v>0.5105940112000001</v>
       </c>
       <c r="P23">
-        <v>1.3189271184</v>
+        <v>1.3129560288</v>
       </c>
       <c r="Q23">
-        <v>1.8029271184</v>
+        <v>1.7969560288</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08830962746132642</v>
+        <v>0.08872653838480866</v>
       </c>
       <c r="T23">
-        <v>0.9817465926403335</v>
+        <v>0.9913750204343804</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.51835719516634</v>
+        <v>10.99479550447695</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07741181994015076</v>
+        <v>0.07722687418585364</v>
       </c>
       <c r="C24">
-        <v>12.78159621872633</v>
+        <v>12.65018134367545</v>
       </c>
       <c r="D24">
-        <v>15.24379621872633</v>
+        <v>15.27248134367545</v>
       </c>
       <c r="E24">
-        <v>1.1122</v>
+        <v>1.2723</v>
       </c>
       <c r="F24">
-        <v>3.5222</v>
+        <v>3.6823</v>
       </c>
       <c r="G24">
         <v>1.06</v>
@@ -3368,28 +3368,28 @@
         <v>2.006</v>
       </c>
       <c r="M24">
-        <v>0.18244996</v>
+        <v>0.19074314</v>
       </c>
       <c r="N24">
-        <v>1.82355004</v>
+        <v>1.81525686</v>
       </c>
       <c r="O24">
-        <v>0.5105940112000001</v>
+        <v>0.5082719208000002</v>
       </c>
       <c r="P24">
-        <v>1.3129560288</v>
+        <v>1.3069849392</v>
       </c>
       <c r="Q24">
-        <v>1.7969560288</v>
+        <v>1.7909849392</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08872653838480866</v>
+        <v>0.08915427816344627</v>
       </c>
       <c r="T24">
-        <v>0.9913750204343804</v>
+        <v>1.001253537262039</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.99479550447695</v>
+        <v>10.51676091732578</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07722687418585364</v>
+        <v>0.07704192843155649</v>
       </c>
       <c r="C25">
-        <v>12.65018134367545</v>
+        <v>12.5188746290433</v>
       </c>
       <c r="D25">
-        <v>15.27248134367545</v>
+        <v>15.3012746290433</v>
       </c>
       <c r="E25">
-        <v>1.2723</v>
+        <v>1.4324</v>
       </c>
       <c r="F25">
-        <v>3.6823</v>
+        <v>3.8424</v>
       </c>
       <c r="G25">
         <v>1.06</v>
@@ -3450,28 +3450,28 @@
         <v>2.006</v>
       </c>
       <c r="M25">
-        <v>0.19074314</v>
+        <v>0.19903632</v>
       </c>
       <c r="N25">
-        <v>1.81525686</v>
+        <v>1.80696368</v>
       </c>
       <c r="O25">
-        <v>0.5082719208000002</v>
+        <v>0.5059498304000001</v>
       </c>
       <c r="P25">
-        <v>1.3069849392</v>
+        <v>1.3010138496</v>
       </c>
       <c r="Q25">
-        <v>1.7909849392</v>
+        <v>1.7850138496</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08915427816344627</v>
+        <v>0.08959327425204804</v>
       </c>
       <c r="T25">
-        <v>1.001253537262039</v>
+        <v>1.011392015058846</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.51676091732578</v>
+        <v>10.07856254577054</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07704192843155649</v>
+        <v>0.07716298267725938</v>
       </c>
       <c r="C26">
-        <v>12.5188746290433</v>
+        <v>12.33991603565931</v>
       </c>
       <c r="D26">
-        <v>15.3012746290433</v>
+        <v>15.28241603565931</v>
       </c>
       <c r="E26">
-        <v>1.432399999999999</v>
+        <v>1.592499999999999</v>
       </c>
       <c r="F26">
-        <v>3.8424</v>
+        <v>4.0025</v>
       </c>
       <c r="G26">
         <v>1.06</v>
@@ -3532,45 +3532,45 @@
         <v>2.006</v>
       </c>
       <c r="M26">
-        <v>0.19903632</v>
+        <v>0.21413375</v>
       </c>
       <c r="N26">
-        <v>1.80696368</v>
+        <v>1.79186625</v>
       </c>
       <c r="O26">
-        <v>0.5059498304000001</v>
+        <v>0.5017225500000001</v>
       </c>
       <c r="P26">
-        <v>1.3010138496</v>
+        <v>1.2901437</v>
       </c>
       <c r="Q26">
-        <v>1.7850138496</v>
+        <v>1.7741437</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08959327425204804</v>
+        <v>0.0900439769030125</v>
       </c>
       <c r="T26">
-        <v>1.011392015058846</v>
+        <v>1.021800852263568</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.28</v>
       </c>
       <c r="W26">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.07856254577054</v>
+        <v>9.367976790207058</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07716298267725938</v>
+        <v>0.07699027692296226</v>
       </c>
       <c r="C27">
-        <v>12.33991603565931</v>
+        <v>12.20673540036435</v>
       </c>
       <c r="D27">
-        <v>15.28241603565931</v>
+        <v>15.30933540036435</v>
       </c>
       <c r="E27">
-        <v>1.592499999999999</v>
+        <v>1.752599999999999</v>
       </c>
       <c r="F27">
-        <v>4.0025</v>
+        <v>4.162599999999999</v>
       </c>
       <c r="G27">
         <v>1.06</v>
@@ -3614,28 +3614,28 @@
         <v>2.006</v>
       </c>
       <c r="M27">
-        <v>0.21413375</v>
+        <v>0.2226991</v>
       </c>
       <c r="N27">
-        <v>1.79186625</v>
+        <v>1.7833009</v>
       </c>
       <c r="O27">
-        <v>0.5017225500000001</v>
+        <v>0.4993242520000001</v>
       </c>
       <c r="P27">
-        <v>1.2901437</v>
+        <v>1.283976648</v>
       </c>
       <c r="Q27">
-        <v>1.7741437</v>
+        <v>1.767976648</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0900439769030125</v>
+        <v>0.09050686070670574</v>
       </c>
       <c r="T27">
-        <v>1.021800852263568</v>
+        <v>1.032491009392743</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.367976790207058</v>
+        <v>9.007669990583709</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07699027692296226</v>
+        <v>0.07681757116866512</v>
       </c>
       <c r="C28">
-        <v>12.20673540036435</v>
+        <v>12.07364976718066</v>
       </c>
       <c r="D28">
-        <v>15.30933540036435</v>
+        <v>15.33634976718066</v>
       </c>
       <c r="E28">
-        <v>1.752599999999999</v>
+        <v>1.912699999999999</v>
       </c>
       <c r="F28">
-        <v>4.162599999999999</v>
+        <v>4.322699999999999</v>
       </c>
       <c r="G28">
         <v>1.06</v>
@@ -3696,28 +3696,28 @@
         <v>2.006</v>
       </c>
       <c r="M28">
-        <v>0.2226991</v>
+        <v>0.23126445</v>
       </c>
       <c r="N28">
-        <v>1.7833009</v>
+        <v>1.77473555</v>
       </c>
       <c r="O28">
-        <v>0.4993242520000001</v>
+        <v>0.4969259540000002</v>
       </c>
       <c r="P28">
-        <v>1.283976648</v>
+        <v>1.277809596</v>
       </c>
       <c r="Q28">
-        <v>1.767976648</v>
+        <v>1.761809596</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09050686070670574</v>
+        <v>0.09098242625844538</v>
       </c>
       <c r="T28">
-        <v>1.032491009392743</v>
+        <v>1.043474047539154</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.007669990583709</v>
+        <v>8.674052583525054</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07681757116866512</v>
+        <v>0.076644865414368</v>
       </c>
       <c r="C29">
-        <v>12.07364976718066</v>
+        <v>11.94065963991035</v>
       </c>
       <c r="D29">
-        <v>15.33634976718066</v>
+        <v>15.36345963991035</v>
       </c>
       <c r="E29">
-        <v>1.912699999999999</v>
+        <v>2.0728</v>
       </c>
       <c r="F29">
-        <v>4.322699999999999</v>
+        <v>4.4828</v>
       </c>
       <c r="G29">
         <v>1.06</v>
@@ -3778,28 +3778,28 @@
         <v>2.006</v>
       </c>
       <c r="M29">
-        <v>0.23126445</v>
+        <v>0.2398298</v>
       </c>
       <c r="N29">
-        <v>1.77473555</v>
+        <v>1.7661702</v>
       </c>
       <c r="O29">
-        <v>0.4969259540000002</v>
+        <v>0.4945276560000001</v>
       </c>
       <c r="P29">
-        <v>1.277809596</v>
+        <v>1.271642544</v>
       </c>
       <c r="Q29">
-        <v>1.761809596</v>
+        <v>1.755642544</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09098242625844538</v>
+        <v>0.09147120196440001</v>
       </c>
       <c r="T29">
-        <v>1.043474047539154</v>
+        <v>1.054762170078522</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.674052583525054</v>
+        <v>8.364264991256299</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.076644865414368</v>
+        <v>0.07647215966007087</v>
       </c>
       <c r="C30">
-        <v>11.94065963991035</v>
+        <v>11.80776552592411</v>
       </c>
       <c r="D30">
-        <v>15.36345963991035</v>
+        <v>15.39066552592412</v>
       </c>
       <c r="E30">
-        <v>2.0728</v>
+        <v>2.2329</v>
       </c>
       <c r="F30">
-        <v>4.4828</v>
+        <v>4.6429</v>
       </c>
       <c r="G30">
         <v>1.06</v>
@@ -3860,28 +3860,28 @@
         <v>2.006</v>
       </c>
       <c r="M30">
-        <v>0.2398298</v>
+        <v>0.24839515</v>
       </c>
       <c r="N30">
-        <v>1.7661702</v>
+        <v>1.75760485</v>
       </c>
       <c r="O30">
-        <v>0.4945276560000001</v>
+        <v>0.4921293580000001</v>
       </c>
       <c r="P30">
-        <v>1.271642544</v>
+        <v>1.265475492</v>
       </c>
       <c r="Q30">
-        <v>1.755642544</v>
+        <v>1.749475492</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09147120196440001</v>
+        <v>0.09197374600009983</v>
       </c>
       <c r="T30">
-        <v>1.054762170078522</v>
+        <v>1.066368267900689</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.364264991256299</v>
+        <v>8.075842060523325</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07647215966007087</v>
+        <v>0.07629945390577375</v>
       </c>
       <c r="C31">
-        <v>11.80776552592412</v>
+        <v>11.67496793619285</v>
       </c>
       <c r="D31">
-        <v>15.39066552592412</v>
+        <v>15.41796793619285</v>
       </c>
       <c r="E31">
-        <v>2.232899999999999</v>
+        <v>2.392999999999999</v>
       </c>
       <c r="F31">
-        <v>4.642899999999999</v>
+        <v>4.802999999999999</v>
       </c>
       <c r="G31">
         <v>1.06</v>
@@ -3942,28 +3942,28 @@
         <v>2.006</v>
       </c>
       <c r="M31">
-        <v>0.24839515</v>
+        <v>0.2569604999999999</v>
       </c>
       <c r="N31">
-        <v>1.75760485</v>
+        <v>1.7490395</v>
       </c>
       <c r="O31">
-        <v>0.4921293580000001</v>
+        <v>0.4897310600000001</v>
       </c>
       <c r="P31">
-        <v>1.265475492</v>
+        <v>1.25930844</v>
       </c>
       <c r="Q31">
-        <v>1.749475492</v>
+        <v>1.74330844</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09197374600009983</v>
+        <v>0.09249064843681966</v>
       </c>
       <c r="T31">
-        <v>1.066368267900689</v>
+        <v>1.078305968517775</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.075842060523325</v>
+        <v>7.806647325172549</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07629945390577375</v>
+        <v>0.07630530815147663</v>
       </c>
       <c r="C32">
-        <v>11.67496793619285</v>
+        <v>11.51394087425618</v>
       </c>
       <c r="D32">
-        <v>15.41796793619285</v>
+        <v>15.41704087425618</v>
       </c>
       <c r="E32">
-        <v>2.392999999999999</v>
+        <v>2.553099999999999</v>
       </c>
       <c r="F32">
-        <v>4.802999999999999</v>
+        <v>4.963099999999999</v>
       </c>
       <c r="G32">
         <v>1.06</v>
@@ -4024,45 +4024,45 @@
         <v>2.006</v>
       </c>
       <c r="M32">
-        <v>0.2569604999999999</v>
+        <v>0.26949633</v>
       </c>
       <c r="N32">
-        <v>1.7490395</v>
+        <v>1.73650367</v>
       </c>
       <c r="O32">
-        <v>0.4897310600000001</v>
+        <v>0.4862210276000001</v>
       </c>
       <c r="P32">
-        <v>1.25930844</v>
+        <v>1.2502826424</v>
       </c>
       <c r="Q32">
-        <v>1.74330844</v>
+        <v>1.7342826424</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09249064843681966</v>
+        <v>0.09302253355286469</v>
       </c>
       <c r="T32">
-        <v>1.078305968517775</v>
+        <v>1.090589689442603</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.28</v>
       </c>
       <c r="W32">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.806647325172549</v>
+        <v>7.443515093507955</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07630530815147663</v>
+        <v>0.0761383623971795</v>
       </c>
       <c r="C33">
-        <v>11.51394087425618</v>
+        <v>11.3803217527783</v>
       </c>
       <c r="D33">
-        <v>15.41704087425618</v>
+        <v>15.4435217527783</v>
       </c>
       <c r="E33">
-        <v>2.553099999999999</v>
+        <v>2.7132</v>
       </c>
       <c r="F33">
-        <v>4.963099999999999</v>
+        <v>5.1232</v>
       </c>
       <c r="G33">
         <v>1.06</v>
@@ -4106,28 +4106,28 @@
         <v>2.006</v>
       </c>
       <c r="M33">
-        <v>0.26949633</v>
+        <v>0.27818976</v>
       </c>
       <c r="N33">
-        <v>1.73650367</v>
+        <v>1.72781024</v>
       </c>
       <c r="O33">
-        <v>0.4862210276000001</v>
+        <v>0.4837868672000001</v>
       </c>
       <c r="P33">
-        <v>1.2502826424</v>
+        <v>1.2440233728</v>
       </c>
       <c r="Q33">
-        <v>1.7342826424</v>
+        <v>1.7280233728</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09302253355286469</v>
+        <v>0.09357006234879339</v>
       </c>
       <c r="T33">
-        <v>1.090589689442603</v>
+        <v>1.103234696276984</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.443515093507955</v>
+        <v>7.210905246835829</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0761383623971795</v>
+        <v>0.07597141664288237</v>
       </c>
       <c r="C34">
-        <v>11.3803217527783</v>
+        <v>11.24679375689007</v>
       </c>
       <c r="D34">
-        <v>15.4435217527783</v>
+        <v>15.47009375689007</v>
       </c>
       <c r="E34">
-        <v>2.7132</v>
+        <v>2.8733</v>
       </c>
       <c r="F34">
-        <v>5.1232</v>
+        <v>5.2833</v>
       </c>
       <c r="G34">
         <v>1.06</v>
@@ -4188,28 +4188,28 @@
         <v>2.006</v>
       </c>
       <c r="M34">
-        <v>0.27818976</v>
+        <v>0.28688319</v>
       </c>
       <c r="N34">
-        <v>1.72781024</v>
+        <v>1.71911681</v>
       </c>
       <c r="O34">
-        <v>0.4837868672000001</v>
+        <v>0.4813527068000001</v>
       </c>
       <c r="P34">
-        <v>1.2440233728</v>
+        <v>1.2377641032</v>
       </c>
       <c r="Q34">
-        <v>1.7280233728</v>
+        <v>1.7217641032</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09357006234879339</v>
+        <v>0.09413393528788415</v>
       </c>
       <c r="T34">
-        <v>1.103234696276984</v>
+        <v>1.116257166001944</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.210905246835829</v>
+        <v>6.992392966628683</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07597141664288237</v>
+        <v>0.07580447088858525</v>
       </c>
       <c r="C35">
-        <v>11.24679375689007</v>
+        <v>11.11335735777215</v>
       </c>
       <c r="D35">
-        <v>15.47009375689007</v>
+        <v>15.49675735777215</v>
       </c>
       <c r="E35">
-        <v>2.8733</v>
+        <v>3.033399999999999</v>
       </c>
       <c r="F35">
-        <v>5.2833</v>
+        <v>5.4434</v>
       </c>
       <c r="G35">
         <v>1.06</v>
@@ -4270,28 +4270,28 @@
         <v>2.006</v>
       </c>
       <c r="M35">
-        <v>0.28688319</v>
+        <v>0.29557662</v>
       </c>
       <c r="N35">
-        <v>1.71911681</v>
+        <v>1.71042338</v>
       </c>
       <c r="O35">
-        <v>0.4813527068000001</v>
+        <v>0.4789185464000001</v>
       </c>
       <c r="P35">
-        <v>1.2377641032</v>
+        <v>1.2315048336</v>
       </c>
       <c r="Q35">
-        <v>1.7217641032</v>
+        <v>1.7155048336</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09413393528788415</v>
+        <v>0.09471489528573523</v>
       </c>
       <c r="T35">
-        <v>1.116257166001944</v>
+        <v>1.129674256021599</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.992392966628683</v>
+        <v>6.786734349963135</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07580447088858525</v>
+        <v>0.07563752513428813</v>
       </c>
       <c r="C36">
-        <v>11.11335735777215</v>
+        <v>10.98001302985924</v>
       </c>
       <c r="D36">
-        <v>15.49675735777215</v>
+        <v>15.52351302985924</v>
       </c>
       <c r="E36">
-        <v>3.033399999999999</v>
+        <v>3.193499999999999</v>
       </c>
       <c r="F36">
-        <v>5.4434</v>
+        <v>5.603499999999999</v>
       </c>
       <c r="G36">
         <v>1.06</v>
@@ -4352,28 +4352,28 @@
         <v>2.006</v>
       </c>
       <c r="M36">
-        <v>0.29557662</v>
+        <v>0.30427005</v>
       </c>
       <c r="N36">
-        <v>1.71042338</v>
+        <v>1.70172995</v>
       </c>
       <c r="O36">
-        <v>0.4789185464000001</v>
+        <v>0.4764843860000001</v>
       </c>
       <c r="P36">
-        <v>1.2315048336</v>
+        <v>1.225245564</v>
       </c>
       <c r="Q36">
-        <v>1.7155048336</v>
+        <v>1.709245564</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09471489528573523</v>
+        <v>0.0953137309758279</v>
       </c>
       <c r="T36">
-        <v>1.129674256021599</v>
+        <v>1.143504179580321</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.786734349963135</v>
+        <v>6.592827654249902</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07563752513428813</v>
+        <v>0.07547057937999099</v>
       </c>
       <c r="C37">
-        <v>10.98001302985924</v>
+        <v>10.84676125086823</v>
       </c>
       <c r="D37">
-        <v>15.52351302985924</v>
+        <v>15.55036125086823</v>
       </c>
       <c r="E37">
-        <v>3.193499999999999</v>
+        <v>3.3536</v>
       </c>
       <c r="F37">
-        <v>5.603499999999999</v>
+        <v>5.7636</v>
       </c>
       <c r="G37">
         <v>1.06</v>
@@ -4434,28 +4434,28 @@
         <v>2.006</v>
       </c>
       <c r="M37">
-        <v>0.30427005</v>
+        <v>0.31296348</v>
       </c>
       <c r="N37">
-        <v>1.70172995</v>
+        <v>1.69303652</v>
       </c>
       <c r="O37">
-        <v>0.4764843860000001</v>
+        <v>0.4740502256000001</v>
       </c>
       <c r="P37">
-        <v>1.225245564</v>
+        <v>1.2189862944</v>
       </c>
       <c r="Q37">
-        <v>1.709245564</v>
+        <v>1.7029862944</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0953137309758279</v>
+        <v>0.09593128028123594</v>
       </c>
       <c r="T37">
-        <v>1.143504179580321</v>
+        <v>1.157766288250253</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.592827654249902</v>
+        <v>6.409693552742959</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07547057937999101</v>
+        <v>0.07530363362569388</v>
       </c>
       <c r="C38">
-        <v>10.84676125086823</v>
+        <v>10.7136025018266</v>
       </c>
       <c r="D38">
-        <v>15.55036125086823</v>
+        <v>15.5773025018266</v>
       </c>
       <c r="E38">
-        <v>3.353599999999999</v>
+        <v>3.513699999999999</v>
       </c>
       <c r="F38">
-        <v>5.763599999999999</v>
+        <v>5.923699999999999</v>
       </c>
       <c r="G38">
         <v>1.06</v>
@@ -4516,28 +4516,28 @@
         <v>2.006</v>
       </c>
       <c r="M38">
-        <v>0.31296348</v>
+        <v>0.32165691</v>
       </c>
       <c r="N38">
-        <v>1.69303652</v>
+        <v>1.68434309</v>
       </c>
       <c r="O38">
-        <v>0.4740502256000001</v>
+        <v>0.4716160652000001</v>
       </c>
       <c r="P38">
-        <v>1.2189862944</v>
+        <v>1.2127270248</v>
       </c>
       <c r="Q38">
-        <v>1.7029862944</v>
+        <v>1.6967270248</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09593128028123594</v>
+        <v>0.09656843432649823</v>
       </c>
       <c r="T38">
-        <v>1.157766288250253</v>
+        <v>1.172481162274786</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.409693552742961</v>
+        <v>6.236458591858016</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07530363362569388</v>
+        <v>0.07541028787139675</v>
       </c>
       <c r="C39">
-        <v>10.7136025018266</v>
+        <v>10.53628017307848</v>
       </c>
       <c r="D39">
-        <v>15.5773025018266</v>
+        <v>15.56008017307848</v>
       </c>
       <c r="E39">
-        <v>3.513699999999999</v>
+        <v>3.673799999999999</v>
       </c>
       <c r="F39">
-        <v>5.923699999999999</v>
+        <v>6.083799999999999</v>
       </c>
       <c r="G39">
         <v>1.06</v>
@@ -4598,45 +4598,45 @@
         <v>2.006</v>
       </c>
       <c r="M39">
-        <v>0.32165691</v>
+        <v>0.33643414</v>
       </c>
       <c r="N39">
-        <v>1.68434309</v>
+        <v>1.66956586</v>
       </c>
       <c r="O39">
-        <v>0.4716160652000001</v>
+        <v>0.4674784408000001</v>
       </c>
       <c r="P39">
-        <v>1.2127270248</v>
+        <v>1.2020874192</v>
       </c>
       <c r="Q39">
-        <v>1.6967270248</v>
+        <v>1.6860874192</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09656843432649823</v>
+        <v>0.09722614172805928</v>
       </c>
       <c r="T39">
-        <v>1.172481162274786</v>
+        <v>1.187670709654949</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.28</v>
       </c>
       <c r="W39">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.236458591858016</v>
+        <v>5.962534004426543</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07541028787139675</v>
+        <v>0.07525054211709963</v>
       </c>
       <c r="C40">
-        <v>10.53628017307848</v>
+        <v>10.40198983996942</v>
       </c>
       <c r="D40">
-        <v>15.56008017307848</v>
+        <v>15.58588983996942</v>
       </c>
       <c r="E40">
-        <v>3.673799999999999</v>
+        <v>3.833899999999999</v>
       </c>
       <c r="F40">
-        <v>6.083799999999999</v>
+        <v>6.243899999999999</v>
       </c>
       <c r="G40">
         <v>1.06</v>
@@ -4680,28 +4680,28 @@
         <v>2.006</v>
       </c>
       <c r="M40">
-        <v>0.33643414</v>
+        <v>0.34528767</v>
       </c>
       <c r="N40">
-        <v>1.66956586</v>
+        <v>1.66071233</v>
       </c>
       <c r="O40">
-        <v>0.4674784408000001</v>
+        <v>0.4649994524000001</v>
       </c>
       <c r="P40">
-        <v>1.2020874192</v>
+        <v>1.1957128776</v>
       </c>
       <c r="Q40">
-        <v>1.6860874192</v>
+        <v>1.6797128776</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09722614172805928</v>
+        <v>0.0979054133067207</v>
       </c>
       <c r="T40">
-        <v>1.187670709654949</v>
+        <v>1.203358274982003</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.962534004426543</v>
+        <v>5.809648517133555</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07525054211709963</v>
+        <v>0.0750907963628025</v>
       </c>
       <c r="C41">
-        <v>10.40198983996942</v>
+        <v>10.2677852706437</v>
       </c>
       <c r="D41">
-        <v>15.58588983996942</v>
+        <v>15.6117852706437</v>
       </c>
       <c r="E41">
-        <v>3.833899999999999</v>
+        <v>3.994</v>
       </c>
       <c r="F41">
-        <v>6.243899999999999</v>
+        <v>6.404</v>
       </c>
       <c r="G41">
         <v>1.06</v>
@@ -4762,28 +4762,28 @@
         <v>2.006</v>
       </c>
       <c r="M41">
-        <v>0.34528767</v>
+        <v>0.3541412</v>
       </c>
       <c r="N41">
-        <v>1.66071233</v>
+        <v>1.6518588</v>
       </c>
       <c r="O41">
-        <v>0.4649994524000001</v>
+        <v>0.4625204640000001</v>
       </c>
       <c r="P41">
-        <v>1.1957128776</v>
+        <v>1.189338336</v>
       </c>
       <c r="Q41">
-        <v>1.6797128776</v>
+        <v>1.673338336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0979054133067207</v>
+        <v>0.0986073272713375</v>
       </c>
       <c r="T41">
-        <v>1.203358274982003</v>
+        <v>1.219568759153291</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.809648517133555</v>
+        <v>5.664407304205216</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0750907963628025</v>
+        <v>0.07493105060850537</v>
       </c>
       <c r="C42">
-        <v>10.2677852706437</v>
+        <v>10.13366689329366</v>
       </c>
       <c r="D42">
-        <v>15.6117852706437</v>
+        <v>15.63776689329366</v>
       </c>
       <c r="E42">
-        <v>3.994</v>
+        <v>4.1541</v>
       </c>
       <c r="F42">
-        <v>6.404</v>
+        <v>6.5641</v>
       </c>
       <c r="G42">
         <v>1.06</v>
@@ -4844,28 +4844,28 @@
         <v>2.006</v>
       </c>
       <c r="M42">
-        <v>0.3541412</v>
+        <v>0.36299473</v>
       </c>
       <c r="N42">
-        <v>1.6518588</v>
+        <v>1.64300527</v>
       </c>
       <c r="O42">
-        <v>0.4625204640000001</v>
+        <v>0.4600414756000001</v>
       </c>
       <c r="P42">
-        <v>1.189338336</v>
+        <v>1.1829637944</v>
       </c>
       <c r="Q42">
-        <v>1.673338336</v>
+        <v>1.6669637944</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0986073272713375</v>
+        <v>0.09933303492967013</v>
       </c>
       <c r="T42">
-        <v>1.219568759153291</v>
+        <v>1.23632875126259</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.664407304205216</v>
+        <v>5.526251028492894</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07493105060850537</v>
+        <v>0.07477130485420824</v>
       </c>
       <c r="C43">
-        <v>10.13366689329366</v>
+        <v>9.999635138966816</v>
       </c>
       <c r="D43">
-        <v>15.63776689329366</v>
+        <v>15.66383513896682</v>
       </c>
       <c r="E43">
-        <v>4.1541</v>
+        <v>4.3142</v>
       </c>
       <c r="F43">
-        <v>6.5641</v>
+        <v>6.7242</v>
       </c>
       <c r="G43">
         <v>1.06</v>
@@ -4926,28 +4926,28 @@
         <v>2.006</v>
       </c>
       <c r="M43">
-        <v>0.36299473</v>
+        <v>0.37184826</v>
       </c>
       <c r="N43">
-        <v>1.64300527</v>
+        <v>1.63415174</v>
       </c>
       <c r="O43">
-        <v>0.4600414756000001</v>
+        <v>0.4575624872000001</v>
       </c>
       <c r="P43">
-        <v>1.1829637944</v>
+        <v>1.1765892528</v>
       </c>
       <c r="Q43">
-        <v>1.6669637944</v>
+        <v>1.6605892528</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09933303492967013</v>
+        <v>0.1000837669900142</v>
       </c>
       <c r="T43">
-        <v>1.23632875126259</v>
+        <v>1.253666674134278</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.526251028492894</v>
+        <v>5.394673623052587</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07477130485420826</v>
+        <v>0.07461155909991113</v>
       </c>
       <c r="C44">
-        <v>9.999635138966816</v>
+        <v>9.865690441589742</v>
       </c>
       <c r="D44">
-        <v>15.66383513896682</v>
+        <v>15.68999044158974</v>
       </c>
       <c r="E44">
-        <v>4.314199999999999</v>
+        <v>4.474299999999999</v>
       </c>
       <c r="F44">
-        <v>6.724199999999999</v>
+        <v>6.884299999999999</v>
       </c>
       <c r="G44">
         <v>1.06</v>
@@ -5008,28 +5008,28 @@
         <v>2.006</v>
       </c>
       <c r="M44">
-        <v>0.3718482599999999</v>
+        <v>0.3807017899999999</v>
       </c>
       <c r="N44">
-        <v>1.63415174</v>
+        <v>1.62529821</v>
       </c>
       <c r="O44">
-        <v>0.4575624872000001</v>
+        <v>0.4550834988000002</v>
       </c>
       <c r="P44">
-        <v>1.1765892528</v>
+        <v>1.1702147112</v>
       </c>
       <c r="Q44">
-        <v>1.6605892528</v>
+        <v>1.6542147112</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1000837669900142</v>
+        <v>0.1008608405261599</v>
       </c>
       <c r="T44">
-        <v>1.253666674134278</v>
+        <v>1.271612945176903</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.394673623052587</v>
+        <v>5.269216096935086</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07461155909991113</v>
+        <v>0.07445181334561402</v>
       </c>
       <c r="C45">
-        <v>9.865690441589742</v>
+        <v>9.73183323799211</v>
       </c>
       <c r="D45">
-        <v>15.68999044158974</v>
+        <v>15.71623323799211</v>
       </c>
       <c r="E45">
-        <v>4.474299999999999</v>
+        <v>4.634399999999999</v>
       </c>
       <c r="F45">
-        <v>6.884299999999999</v>
+        <v>7.0444</v>
       </c>
       <c r="G45">
         <v>1.06</v>
@@ -5090,28 +5090,28 @@
         <v>2.006</v>
       </c>
       <c r="M45">
-        <v>0.3807017899999999</v>
+        <v>0.38955532</v>
       </c>
       <c r="N45">
-        <v>1.62529821</v>
+        <v>1.61644468</v>
       </c>
       <c r="O45">
-        <v>0.4550834988000002</v>
+        <v>0.4526045104000001</v>
       </c>
       <c r="P45">
-        <v>1.1702147112</v>
+        <v>1.1638401696</v>
       </c>
       <c r="Q45">
-        <v>1.6542147112</v>
+        <v>1.6478401696</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1008608405261599</v>
+        <v>0.1016656666885964</v>
       </c>
       <c r="T45">
-        <v>1.271612945176903</v>
+        <v>1.29020015447105</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.269216096935086</v>
+        <v>5.149461185641106</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07445181334561402</v>
+        <v>0.07429206759131687</v>
       </c>
       <c r="C46">
-        <v>9.73183323799211</v>
+        <v>9.598063967931026</v>
       </c>
       <c r="D46">
-        <v>15.71623323799211</v>
+        <v>15.74256396793103</v>
       </c>
       <c r="E46">
-        <v>4.634399999999999</v>
+        <v>4.794499999999999</v>
       </c>
       <c r="F46">
-        <v>7.0444</v>
+        <v>7.204499999999999</v>
       </c>
       <c r="G46">
         <v>1.06</v>
@@ -5172,28 +5172,28 @@
         <v>2.006</v>
       </c>
       <c r="M46">
-        <v>0.38955532</v>
+        <v>0.39840885</v>
       </c>
       <c r="N46">
-        <v>1.61644468</v>
+        <v>1.60759115</v>
       </c>
       <c r="O46">
-        <v>0.4526045104000001</v>
+        <v>0.4501255220000001</v>
       </c>
       <c r="P46">
-        <v>1.1638401696</v>
+        <v>1.157465628</v>
       </c>
       <c r="Q46">
-        <v>1.6478401696</v>
+        <v>1.641465628</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1016656666885964</v>
+        <v>0.1024997592569398</v>
       </c>
       <c r="T46">
-        <v>1.29020015447105</v>
+        <v>1.309463262284984</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.149461185641106</v>
+        <v>5.035028714849081</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07429206759131687</v>
+        <v>0.07413232183701975</v>
       </c>
       <c r="C47">
-        <v>9.598063967931026</v>
+        <v>9.464383074115592</v>
       </c>
       <c r="D47">
-        <v>15.74256396793103</v>
+        <v>15.76898307411559</v>
       </c>
       <c r="E47">
-        <v>4.794499999999999</v>
+        <v>4.954599999999999</v>
       </c>
       <c r="F47">
-        <v>7.204499999999999</v>
+        <v>7.364599999999999</v>
       </c>
       <c r="G47">
         <v>1.06</v>
@@ -5254,28 +5254,28 @@
         <v>2.006</v>
       </c>
       <c r="M47">
-        <v>0.39840885</v>
+        <v>0.40726238</v>
       </c>
       <c r="N47">
-        <v>1.60759115</v>
+        <v>1.59873762</v>
       </c>
       <c r="O47">
-        <v>0.4501255220000001</v>
+        <v>0.4476465336000001</v>
       </c>
       <c r="P47">
-        <v>1.157465628</v>
+        <v>1.1510910864</v>
       </c>
       <c r="Q47">
-        <v>1.641465628</v>
+        <v>1.6350910864</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1024997592569398</v>
+        <v>0.1033647441426292</v>
       </c>
       <c r="T47">
-        <v>1.309463262284984</v>
+        <v>1.329439818536471</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.035028714849081</v>
+        <v>4.925571568874101</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07413232183701975</v>
+        <v>0.07397257608272263</v>
       </c>
       <c r="C48">
-        <v>9.464383074115592</v>
+        <v>9.330791002231706</v>
       </c>
       <c r="D48">
-        <v>15.76898307411559</v>
+        <v>15.7954910022317</v>
       </c>
       <c r="E48">
-        <v>4.954599999999999</v>
+        <v>5.114699999999999</v>
       </c>
       <c r="F48">
-        <v>7.364599999999999</v>
+        <v>7.524699999999999</v>
       </c>
       <c r="G48">
         <v>1.06</v>
@@ -5336,28 +5336,28 @@
         <v>2.006</v>
       </c>
       <c r="M48">
-        <v>0.40726238</v>
+        <v>0.41611591</v>
       </c>
       <c r="N48">
-        <v>1.59873762</v>
+        <v>1.58988409</v>
       </c>
       <c r="O48">
-        <v>0.4476465336000001</v>
+        <v>0.4451675452000001</v>
       </c>
       <c r="P48">
-        <v>1.1510910864</v>
+        <v>1.1447165448</v>
       </c>
       <c r="Q48">
-        <v>1.6350910864</v>
+        <v>1.6287165448</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1033647441426292</v>
+        <v>0.1042623699674012</v>
       </c>
       <c r="T48">
-        <v>1.329439818536471</v>
+        <v>1.350170207099335</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.925571568874101</v>
+        <v>4.820772173791673</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07397257608272263</v>
+        <v>0.0738128303284255</v>
       </c>
       <c r="C49">
-        <v>9.330791002231706</v>
+        <v>9.197288200967147</v>
       </c>
       <c r="D49">
-        <v>15.7954910022317</v>
+        <v>15.82208820096715</v>
       </c>
       <c r="E49">
-        <v>5.114699999999999</v>
+        <v>5.2748</v>
       </c>
       <c r="F49">
-        <v>7.524699999999999</v>
+        <v>7.6848</v>
       </c>
       <c r="G49">
         <v>1.06</v>
@@ -5418,28 +5418,28 @@
         <v>2.006</v>
       </c>
       <c r="M49">
-        <v>0.41611591</v>
+        <v>0.42496944</v>
       </c>
       <c r="N49">
-        <v>1.58988409</v>
+        <v>1.58103056</v>
       </c>
       <c r="O49">
-        <v>0.4451675452000001</v>
+        <v>0.4426885568000001</v>
       </c>
       <c r="P49">
-        <v>1.1447165448</v>
+        <v>1.1383420032</v>
       </c>
       <c r="Q49">
-        <v>1.6287165448</v>
+        <v>1.6223420032</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1042623699674012</v>
+        <v>0.1051945198623567</v>
       </c>
       <c r="T49">
-        <v>1.350170207099335</v>
+        <v>1.371697918299232</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.820772173791673</v>
+        <v>4.720339420171014</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0738128303284255</v>
+        <v>0.07365308457412838</v>
       </c>
       <c r="C50">
-        <v>9.197288200967147</v>
+        <v>9.063875122036876</v>
       </c>
       <c r="D50">
-        <v>15.82208820096715</v>
+        <v>15.84877512203687</v>
       </c>
       <c r="E50">
-        <v>5.274799999999999</v>
+        <v>5.434899999999999</v>
       </c>
       <c r="F50">
-        <v>7.684799999999999</v>
+        <v>7.844899999999999</v>
       </c>
       <c r="G50">
         <v>1.06</v>
@@ -5500,28 +5500,28 @@
         <v>2.006</v>
       </c>
       <c r="M50">
-        <v>0.42496944</v>
+        <v>0.43382297</v>
       </c>
       <c r="N50">
-        <v>1.58103056</v>
+        <v>1.57217703</v>
       </c>
       <c r="O50">
-        <v>0.4426885568000001</v>
+        <v>0.4402095684000001</v>
       </c>
       <c r="P50">
-        <v>1.1383420032</v>
+        <v>1.1319674616</v>
       </c>
       <c r="Q50">
-        <v>1.6223420032</v>
+        <v>1.6159674616</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1051945198623567</v>
+        <v>0.1061632246551537</v>
       </c>
       <c r="T50">
-        <v>1.371697918299232</v>
+        <v>1.394069853467753</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.720339420171014</v>
+        <v>4.624005962616502</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07365308457412838</v>
+        <v>0.07349333881983125</v>
       </c>
       <c r="C51">
-        <v>9.063875122036876</v>
+        <v>8.930552220208604</v>
       </c>
       <c r="D51">
-        <v>15.84877512203687</v>
+        <v>15.8755522202086</v>
       </c>
       <c r="E51">
-        <v>5.434899999999999</v>
+        <v>5.594999999999999</v>
       </c>
       <c r="F51">
-        <v>7.844899999999999</v>
+        <v>8.004999999999999</v>
       </c>
       <c r="G51">
         <v>1.06</v>
@@ -5582,28 +5582,28 @@
         <v>2.006</v>
       </c>
       <c r="M51">
-        <v>0.43382297</v>
+        <v>0.4426765</v>
       </c>
       <c r="N51">
-        <v>1.57217703</v>
+        <v>1.5633235</v>
       </c>
       <c r="O51">
-        <v>0.4402095684000001</v>
+        <v>0.4377305800000001</v>
       </c>
       <c r="P51">
-        <v>1.1319674616</v>
+        <v>1.12559292</v>
       </c>
       <c r="Q51">
-        <v>1.6159674616</v>
+        <v>1.60959292</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1061632246551537</v>
+        <v>0.1071706776396625</v>
       </c>
       <c r="T51">
-        <v>1.394069853467753</v>
+        <v>1.417336666043014</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.624005962616502</v>
+        <v>4.531525843364173</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07349333881983125</v>
+        <v>0.07425159306553414</v>
       </c>
       <c r="C52">
-        <v>8.930552220208604</v>
+        <v>8.644149357775934</v>
       </c>
       <c r="D52">
-        <v>15.8755522202086</v>
+        <v>15.74924935777593</v>
       </c>
       <c r="E52">
-        <v>5.594999999999999</v>
+        <v>5.755099999999999</v>
       </c>
       <c r="F52">
-        <v>8.004999999999999</v>
+        <v>8.165099999999999</v>
       </c>
       <c r="G52">
         <v>1.06</v>
@@ -5664,45 +5664,45 @@
         <v>2.006</v>
       </c>
       <c r="M52">
-        <v>0.4426765</v>
+        <v>0.47194278</v>
       </c>
       <c r="N52">
-        <v>1.5633235</v>
+        <v>1.53405722</v>
       </c>
       <c r="O52">
-        <v>0.4377305800000001</v>
+        <v>0.4295360216000001</v>
       </c>
       <c r="P52">
-        <v>1.12559292</v>
+        <v>1.1045211984</v>
       </c>
       <c r="Q52">
-        <v>1.60959292</v>
+        <v>1.5885211984</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1071706776396625</v>
+        <v>0.1082192511541513</v>
       </c>
       <c r="T52">
-        <v>1.417336666043014</v>
+        <v>1.441553144437674</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.28</v>
       </c>
       <c r="W52">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.531525843364173</v>
+        <v>4.250515284925008</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07425159306553414</v>
+        <v>0.074109847311237</v>
       </c>
       <c r="C53">
-        <v>8.644149357775934</v>
+        <v>8.50750707781792</v>
       </c>
       <c r="D53">
-        <v>15.74924935777593</v>
+        <v>15.77270707781792</v>
       </c>
       <c r="E53">
-        <v>5.755099999999999</v>
+        <v>5.915199999999999</v>
       </c>
       <c r="F53">
-        <v>8.165099999999999</v>
+        <v>8.325199999999999</v>
       </c>
       <c r="G53">
         <v>1.06</v>
@@ -5746,28 +5746,28 @@
         <v>2.006</v>
       </c>
       <c r="M53">
-        <v>0.47194278</v>
+        <v>0.4811965599999999</v>
       </c>
       <c r="N53">
-        <v>1.53405722</v>
+        <v>1.52480344</v>
       </c>
       <c r="O53">
-        <v>0.4295360216000001</v>
+        <v>0.4269449632000001</v>
       </c>
       <c r="P53">
-        <v>1.1045211984</v>
+        <v>1.0978584768</v>
       </c>
       <c r="Q53">
-        <v>1.5885211984</v>
+        <v>1.5818584768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1082192511541513</v>
+        <v>0.1093115152317438</v>
       </c>
       <c r="T53">
-        <v>1.441553144437674</v>
+        <v>1.466778642765445</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.250515284925008</v>
+        <v>4.168774606368759</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.074109847311237</v>
+        <v>0.07396810155693988</v>
       </c>
       <c r="C54">
-        <v>8.50750707781792</v>
+        <v>8.37093478029923</v>
       </c>
       <c r="D54">
-        <v>15.77270707781792</v>
+        <v>15.79623478029923</v>
       </c>
       <c r="E54">
-        <v>5.915199999999999</v>
+        <v>6.075299999999999</v>
       </c>
       <c r="F54">
-        <v>8.325199999999999</v>
+        <v>8.485299999999999</v>
       </c>
       <c r="G54">
         <v>1.06</v>
@@ -5828,28 +5828,28 @@
         <v>2.006</v>
       </c>
       <c r="M54">
-        <v>0.4811965599999999</v>
+        <v>0.49045034</v>
       </c>
       <c r="N54">
-        <v>1.52480344</v>
+        <v>1.51554966</v>
       </c>
       <c r="O54">
-        <v>0.4269449632000001</v>
+        <v>0.4243539048000001</v>
       </c>
       <c r="P54">
-        <v>1.0978584768</v>
+        <v>1.0911957552</v>
       </c>
       <c r="Q54">
-        <v>1.5818584768</v>
+        <v>1.5751957552</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1093115152317438</v>
+        <v>0.110450258631787</v>
       </c>
       <c r="T54">
-        <v>1.466778642765445</v>
+        <v>1.493077566553972</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.168774606368759</v>
+        <v>4.090118481720291</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07396810155693988</v>
+        <v>0.07382635580264275</v>
       </c>
       <c r="C55">
-        <v>8.37093478029923</v>
+        <v>8.23443277886021</v>
       </c>
       <c r="D55">
-        <v>15.79623478029923</v>
+        <v>15.81983277886021</v>
       </c>
       <c r="E55">
-        <v>6.075299999999999</v>
+        <v>6.235399999999998</v>
       </c>
       <c r="F55">
-        <v>8.485299999999999</v>
+        <v>8.645399999999999</v>
       </c>
       <c r="G55">
         <v>1.06</v>
@@ -5910,28 +5910,28 @@
         <v>2.006</v>
       </c>
       <c r="M55">
-        <v>0.49045034</v>
+        <v>0.49970412</v>
       </c>
       <c r="N55">
-        <v>1.51554966</v>
+        <v>1.50629588</v>
       </c>
       <c r="O55">
-        <v>0.4243539048000001</v>
+        <v>0.4217628464000001</v>
       </c>
       <c r="P55">
-        <v>1.0911957552</v>
+        <v>1.0845330336</v>
       </c>
       <c r="Q55">
-        <v>1.5751957552</v>
+        <v>1.5685330336</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.110450258631787</v>
+        <v>0.1116385126144408</v>
       </c>
       <c r="T55">
-        <v>1.493077566553972</v>
+        <v>1.520519921811565</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.090118481720291</v>
+        <v>4.014375546873618</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07382635580264275</v>
+        <v>0.07507061004834563</v>
       </c>
       <c r="C56">
-        <v>8.23443277886021</v>
+        <v>7.86956367867902</v>
       </c>
       <c r="D56">
-        <v>15.81983277886021</v>
+        <v>15.61506367867902</v>
       </c>
       <c r="E56">
-        <v>6.235399999999998</v>
+        <v>6.3955</v>
       </c>
       <c r="F56">
-        <v>8.645399999999999</v>
+        <v>8.8055</v>
       </c>
       <c r="G56">
         <v>1.06</v>
@@ -5992,45 +5992,45 @@
         <v>2.006</v>
       </c>
       <c r="M56">
-        <v>0.49970412</v>
+        <v>0.53977715</v>
       </c>
       <c r="N56">
-        <v>1.50629588</v>
+        <v>1.46622285</v>
       </c>
       <c r="O56">
-        <v>0.4217628464000001</v>
+        <v>0.4105423980000001</v>
       </c>
       <c r="P56">
-        <v>1.0845330336</v>
+        <v>1.055680452</v>
       </c>
       <c r="Q56">
-        <v>1.5685330336</v>
+        <v>1.539680452</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1116385126144408</v>
+        <v>0.1128795778852125</v>
       </c>
       <c r="T56">
-        <v>1.520519921811565</v>
+        <v>1.54918193730283</v>
       </c>
       <c r="U56">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.28</v>
       </c>
       <c r="W56">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.014375546873618</v>
+        <v>3.716348496782422</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07507061004834563</v>
+        <v>0.07495406429404851</v>
       </c>
       <c r="C57">
-        <v>7.86956367867902</v>
+        <v>7.728418534331871</v>
       </c>
       <c r="D57">
-        <v>15.61506367867902</v>
+        <v>15.63401853433187</v>
       </c>
       <c r="E57">
-        <v>6.3955</v>
+        <v>6.5556</v>
       </c>
       <c r="F57">
-        <v>8.8055</v>
+        <v>8.9656</v>
       </c>
       <c r="G57">
         <v>1.06</v>
@@ -6074,28 +6074,28 @@
         <v>2.006</v>
       </c>
       <c r="M57">
-        <v>0.53977715</v>
+        <v>0.54959128</v>
       </c>
       <c r="N57">
-        <v>1.46622285</v>
+        <v>1.45640872</v>
       </c>
       <c r="O57">
-        <v>0.4105423980000001</v>
+        <v>0.4077944416000001</v>
       </c>
       <c r="P57">
-        <v>1.055680452</v>
+        <v>1.0486142784</v>
       </c>
       <c r="Q57">
-        <v>1.539680452</v>
+        <v>1.5326142784</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1128795778852125</v>
+        <v>0.1141770552137466</v>
       </c>
       <c r="T57">
-        <v>1.54918193730283</v>
+        <v>1.57914677168006</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.716348496782422</v>
+        <v>3.649985130768451</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07495406429404851</v>
+        <v>0.07483751853975137</v>
       </c>
       <c r="C58">
-        <v>7.728418534331871</v>
+        <v>7.587319463855698</v>
       </c>
       <c r="D58">
-        <v>15.63401853433187</v>
+        <v>15.6530194638557</v>
       </c>
       <c r="E58">
-        <v>6.5556</v>
+        <v>6.7157</v>
       </c>
       <c r="F58">
-        <v>8.9656</v>
+        <v>9.1257</v>
       </c>
       <c r="G58">
         <v>1.06</v>
@@ -6156,28 +6156,28 @@
         <v>2.006</v>
       </c>
       <c r="M58">
-        <v>0.54959128</v>
+        <v>0.55940541</v>
       </c>
       <c r="N58">
-        <v>1.45640872</v>
+        <v>1.44659459</v>
       </c>
       <c r="O58">
-        <v>0.4077944416000001</v>
+        <v>0.4050464852000001</v>
       </c>
       <c r="P58">
-        <v>1.0486142784</v>
+        <v>1.0415481048</v>
       </c>
       <c r="Q58">
-        <v>1.5326142784</v>
+        <v>1.5255481048</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1141770552137466</v>
+        <v>0.1155348803250032</v>
       </c>
       <c r="T58">
-        <v>1.57914677168006</v>
+        <v>1.610505319284139</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.649985130768451</v>
+        <v>3.585950303912864</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07483751853975137</v>
+        <v>0.07472097278545425</v>
       </c>
       <c r="C59">
-        <v>7.587319463855698</v>
+        <v>7.446266635443658</v>
       </c>
       <c r="D59">
-        <v>15.6530194638557</v>
+        <v>15.67206663544366</v>
       </c>
       <c r="E59">
-        <v>6.7157</v>
+        <v>6.8758</v>
       </c>
       <c r="F59">
-        <v>9.1257</v>
+        <v>9.2858</v>
       </c>
       <c r="G59">
         <v>1.06</v>
@@ -6238,28 +6238,28 @@
         <v>2.006</v>
       </c>
       <c r="M59">
-        <v>0.55940541</v>
+        <v>0.56921954</v>
       </c>
       <c r="N59">
-        <v>1.44659459</v>
+        <v>1.43678046</v>
       </c>
       <c r="O59">
-        <v>0.4050464852000001</v>
+        <v>0.4022985288000001</v>
       </c>
       <c r="P59">
-        <v>1.0415481048</v>
+        <v>1.0344819312</v>
       </c>
       <c r="Q59">
-        <v>1.5255481048</v>
+        <v>1.5184819312</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1155348803250032</v>
+        <v>0.1169573637748911</v>
       </c>
       <c r="T59">
-        <v>1.610505319284139</v>
+        <v>1.643357131059841</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.585950303912864</v>
+        <v>3.524123574535056</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07472097278545425</v>
+        <v>0.07579386703115712</v>
       </c>
       <c r="C60">
-        <v>7.44626663544366</v>
+        <v>7.11255404869074</v>
       </c>
       <c r="D60">
-        <v>15.67206663544366</v>
+        <v>15.49845404869074</v>
       </c>
       <c r="E60">
-        <v>6.875799999999998</v>
+        <v>7.035899999999998</v>
       </c>
       <c r="F60">
-        <v>9.285799999999998</v>
+        <v>9.445899999999998</v>
       </c>
       <c r="G60">
         <v>1.06</v>
@@ -6320,45 +6320,45 @@
         <v>2.006</v>
       </c>
       <c r="M60">
-        <v>0.5692195399999999</v>
+        <v>0.6054821899999999</v>
       </c>
       <c r="N60">
-        <v>1.43678046</v>
+        <v>1.40051781</v>
       </c>
       <c r="O60">
-        <v>0.4022985288000002</v>
+        <v>0.3921449868000001</v>
       </c>
       <c r="P60">
-        <v>1.0344819312</v>
+        <v>1.0083728232</v>
       </c>
       <c r="Q60">
-        <v>1.5184819312</v>
+        <v>1.4923728232</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1169573637748911</v>
+        <v>0.1184492366613588</v>
       </c>
       <c r="T60">
-        <v>1.64335713105984</v>
+        <v>1.677811470239235</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.28</v>
       </c>
       <c r="W60">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.524123574535057</v>
+        <v>3.313061941590719</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07579386703115712</v>
+        <v>0.07569748127686002</v>
       </c>
       <c r="C61">
-        <v>7.11255404869074</v>
+        <v>6.967893493463837</v>
       </c>
       <c r="D61">
-        <v>15.49845404869074</v>
+        <v>15.51389349346384</v>
       </c>
       <c r="E61">
-        <v>7.035899999999998</v>
+        <v>7.195999999999998</v>
       </c>
       <c r="F61">
-        <v>9.445899999999998</v>
+        <v>9.605999999999998</v>
       </c>
       <c r="G61">
         <v>1.06</v>
@@ -6402,28 +6402,28 @@
         <v>2.006</v>
       </c>
       <c r="M61">
-        <v>0.6054821899999999</v>
+        <v>0.6157445999999999</v>
       </c>
       <c r="N61">
-        <v>1.40051781</v>
+        <v>1.3902554</v>
       </c>
       <c r="O61">
-        <v>0.3921449868000001</v>
+        <v>0.3892715120000002</v>
       </c>
       <c r="P61">
-        <v>1.0083728232</v>
+        <v>1.000983888</v>
       </c>
       <c r="Q61">
-        <v>1.4923728232</v>
+        <v>1.484983888</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1184492366613588</v>
+        <v>0.12001570319215</v>
       </c>
       <c r="T61">
-        <v>1.677811470239235</v>
+        <v>1.713988526377599</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.313061941590719</v>
+        <v>3.257844242564207</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07569748127686002</v>
+        <v>0.07560109552256288</v>
       </c>
       <c r="C62">
-        <v>6.967893493463837</v>
+        <v>6.823263730232043</v>
       </c>
       <c r="D62">
-        <v>15.51389349346384</v>
+        <v>15.52936373023204</v>
       </c>
       <c r="E62">
-        <v>7.195999999999998</v>
+        <v>7.356099999999998</v>
       </c>
       <c r="F62">
-        <v>9.605999999999998</v>
+        <v>9.766099999999998</v>
       </c>
       <c r="G62">
         <v>1.06</v>
@@ -6484,28 +6484,28 @@
         <v>2.006</v>
       </c>
       <c r="M62">
-        <v>0.6157445999999999</v>
+        <v>0.6260070099999999</v>
       </c>
       <c r="N62">
-        <v>1.3902554</v>
+        <v>1.37999299</v>
       </c>
       <c r="O62">
-        <v>0.3892715120000002</v>
+        <v>0.3863980372000001</v>
       </c>
       <c r="P62">
-        <v>1.000983888</v>
+        <v>0.9935949528000002</v>
       </c>
       <c r="Q62">
-        <v>1.484983888</v>
+        <v>1.4775949528</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.12001570319215</v>
+        <v>0.1216625013399048</v>
       </c>
       <c r="T62">
-        <v>1.713988526377599</v>
+        <v>1.752020816164084</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.257844242564207</v>
+        <v>3.20443695989922</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07560109552256288</v>
+        <v>0.07550470976826576</v>
       </c>
       <c r="C63">
-        <v>6.823263730232043</v>
+        <v>6.678664851203319</v>
       </c>
       <c r="D63">
-        <v>15.52936373023204</v>
+        <v>15.54486485120332</v>
       </c>
       <c r="E63">
-        <v>7.356099999999998</v>
+        <v>7.516199999999998</v>
       </c>
       <c r="F63">
-        <v>9.766099999999998</v>
+        <v>9.926199999999998</v>
       </c>
       <c r="G63">
         <v>1.06</v>
@@ -6566,28 +6566,28 @@
         <v>2.006</v>
       </c>
       <c r="M63">
-        <v>0.6260070099999999</v>
+        <v>0.6362694199999999</v>
       </c>
       <c r="N63">
-        <v>1.37999299</v>
+        <v>1.36973058</v>
       </c>
       <c r="O63">
-        <v>0.3863980372000001</v>
+        <v>0.3835245624000002</v>
       </c>
       <c r="P63">
-        <v>0.9935949528000002</v>
+        <v>0.9862060176000003</v>
       </c>
       <c r="Q63">
-        <v>1.4775949528</v>
+        <v>1.4702060176</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1216625013399048</v>
+        <v>0.1233959730743836</v>
       </c>
       <c r="T63">
-        <v>1.752020816164084</v>
+        <v>1.792054805413016</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.20443695989922</v>
+        <v>3.152752492804071</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07550470976826576</v>
+        <v>0.07540832401396863</v>
       </c>
       <c r="C64">
-        <v>6.678664851203319</v>
+        <v>6.534096948954199</v>
       </c>
       <c r="D64">
-        <v>15.54486485120332</v>
+        <v>15.5603969489542</v>
       </c>
       <c r="E64">
-        <v>7.516199999999998</v>
+        <v>7.676299999999999</v>
       </c>
       <c r="F64">
-        <v>9.926199999999998</v>
+        <v>10.0863</v>
       </c>
       <c r="G64">
         <v>1.06</v>
@@ -6648,28 +6648,28 @@
         <v>2.006</v>
       </c>
       <c r="M64">
-        <v>0.6362694199999999</v>
+        <v>0.64653183</v>
       </c>
       <c r="N64">
-        <v>1.36973058</v>
+        <v>1.35946817</v>
       </c>
       <c r="O64">
-        <v>0.3835245624000002</v>
+        <v>0.3806510876000001</v>
       </c>
       <c r="P64">
-        <v>0.9862060176000003</v>
+        <v>0.9788170824000001</v>
       </c>
       <c r="Q64">
-        <v>1.4702060176</v>
+        <v>1.4628170824</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1233959730743836</v>
+        <v>0.125223145983699</v>
       </c>
       <c r="T64">
-        <v>1.792054805413016</v>
+        <v>1.834252794080808</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.152752492804071</v>
+        <v>3.102708802442101</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07540832401396863</v>
+        <v>0.0753119382596715</v>
       </c>
       <c r="C65">
-        <v>6.534096948954199</v>
+        <v>6.389560116431559</v>
       </c>
       <c r="D65">
-        <v>15.5603969489542</v>
+        <v>15.57596011643156</v>
       </c>
       <c r="E65">
-        <v>7.676299999999999</v>
+        <v>7.836399999999999</v>
       </c>
       <c r="F65">
-        <v>10.0863</v>
+        <v>10.2464</v>
       </c>
       <c r="G65">
         <v>1.06</v>
@@ -6730,28 +6730,28 @@
         <v>2.006</v>
       </c>
       <c r="M65">
-        <v>0.64653183</v>
+        <v>0.65679424</v>
       </c>
       <c r="N65">
-        <v>1.35946817</v>
+        <v>1.34920576</v>
       </c>
       <c r="O65">
-        <v>0.3806510876000001</v>
+        <v>0.3777776128000001</v>
       </c>
       <c r="P65">
-        <v>0.9788170824000001</v>
+        <v>0.9714281472000001</v>
       </c>
       <c r="Q65">
-        <v>1.4628170824</v>
+        <v>1.4554281472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.125223145983699</v>
+        <v>0.1271518284990875</v>
       </c>
       <c r="T65">
-        <v>1.834252794080808</v>
+        <v>1.878795115452368</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.102708802442101</v>
+        <v>3.054228977403944</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0753119382596715</v>
+        <v>0.07521555250537437</v>
       </c>
       <c r="C66">
-        <v>6.389560116431559</v>
+        <v>6.245054446954514</v>
       </c>
       <c r="D66">
-        <v>15.57596011643156</v>
+        <v>15.59155444695451</v>
       </c>
       <c r="E66">
-        <v>7.836399999999999</v>
+        <v>7.996499999999999</v>
       </c>
       <c r="F66">
-        <v>10.2464</v>
+        <v>10.4065</v>
       </c>
       <c r="G66">
         <v>1.06</v>
@@ -6812,28 +6812,28 @@
         <v>2.006</v>
       </c>
       <c r="M66">
-        <v>0.65679424</v>
+        <v>0.66705665</v>
       </c>
       <c r="N66">
-        <v>1.34920576</v>
+        <v>1.33894335</v>
       </c>
       <c r="O66">
-        <v>0.3777776128000001</v>
+        <v>0.3749041380000001</v>
       </c>
       <c r="P66">
-        <v>0.9714281472000001</v>
+        <v>0.9640392120000001</v>
       </c>
       <c r="Q66">
-        <v>1.4554281472</v>
+        <v>1.448039212</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1271518284990875</v>
+        <v>0.1291907214439268</v>
       </c>
       <c r="T66">
-        <v>1.878795115452368</v>
+        <v>1.925882712330873</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.054228977403944</v>
+        <v>3.007240839290036</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07521555250537437</v>
+        <v>0.07882572675107724</v>
       </c>
       <c r="C67">
-        <v>6.245054446954514</v>
+        <v>5.521409346639063</v>
       </c>
       <c r="D67">
-        <v>15.59155444695451</v>
+        <v>15.02800934663906</v>
       </c>
       <c r="E67">
-        <v>7.996499999999999</v>
+        <v>8.156599999999999</v>
       </c>
       <c r="F67">
-        <v>10.4065</v>
+        <v>10.5666</v>
       </c>
       <c r="G67">
         <v>1.06</v>
@@ -6894,45 +6894,45 @@
         <v>2.006</v>
       </c>
       <c r="M67">
-        <v>0.66705665</v>
+        <v>0.75973854</v>
       </c>
       <c r="N67">
-        <v>1.33894335</v>
+        <v>1.24626146</v>
       </c>
       <c r="O67">
-        <v>0.3749041380000001</v>
+        <v>0.3489532088000001</v>
       </c>
       <c r="P67">
-        <v>0.9640392120000001</v>
+        <v>0.8973082512000002</v>
       </c>
       <c r="Q67">
-        <v>1.448039212</v>
+        <v>1.3813082512</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1291907214439268</v>
+        <v>0.1313495492678743</v>
       </c>
       <c r="T67">
-        <v>1.925882712330873</v>
+        <v>1.975740167849291</v>
       </c>
       <c r="U67">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V67">
         <v>0.28</v>
       </c>
       <c r="W67">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.007240839290036</v>
+        <v>2.640382045117786</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07882572675107724</v>
+        <v>0.07878550099678014</v>
       </c>
       <c r="C68">
-        <v>5.521409346639063</v>
+        <v>5.367364033556735</v>
       </c>
       <c r="D68">
-        <v>15.02800934663906</v>
+        <v>15.03406403355673</v>
       </c>
       <c r="E68">
-        <v>8.156599999999999</v>
+        <v>8.316699999999999</v>
       </c>
       <c r="F68">
-        <v>10.5666</v>
+        <v>10.7267</v>
       </c>
       <c r="G68">
         <v>1.06</v>
@@ -6976,28 +6976,28 @@
         <v>2.006</v>
       </c>
       <c r="M68">
-        <v>0.75973854</v>
+        <v>0.77124973</v>
       </c>
       <c r="N68">
-        <v>1.24626146</v>
+        <v>1.23475027</v>
       </c>
       <c r="O68">
-        <v>0.3489532088000001</v>
+        <v>0.3457300756000001</v>
       </c>
       <c r="P68">
-        <v>0.8973082512000002</v>
+        <v>0.8890201944</v>
       </c>
       <c r="Q68">
-        <v>1.3813082512</v>
+        <v>1.3730201944</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1313495492678743</v>
+        <v>0.133639215141758</v>
       </c>
       <c r="T68">
-        <v>1.975740167849291</v>
+        <v>2.028619287338522</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.640382045117786</v>
+        <v>2.600973357877221</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07878550099678014</v>
+        <v>0.07874527524248301</v>
       </c>
       <c r="C69">
-        <v>5.367364033556735</v>
+        <v>5.213323601228547</v>
       </c>
       <c r="D69">
-        <v>15.03406403355673</v>
+        <v>15.04012360122855</v>
       </c>
       <c r="E69">
-        <v>8.316699999999999</v>
+        <v>8.476799999999999</v>
       </c>
       <c r="F69">
-        <v>10.7267</v>
+        <v>10.8868</v>
       </c>
       <c r="G69">
         <v>1.06</v>
@@ -7058,28 +7058,28 @@
         <v>2.006</v>
       </c>
       <c r="M69">
-        <v>0.77124973</v>
+        <v>0.78276092</v>
       </c>
       <c r="N69">
-        <v>1.23475027</v>
+        <v>1.22323908</v>
       </c>
       <c r="O69">
-        <v>0.3457300756000001</v>
+        <v>0.3425069424000001</v>
       </c>
       <c r="P69">
-        <v>0.8890201944</v>
+        <v>0.8807321376000002</v>
       </c>
       <c r="Q69">
-        <v>1.3730201944</v>
+        <v>1.3647321376</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.133639215141758</v>
+        <v>0.1360719851327594</v>
       </c>
       <c r="T69">
-        <v>2.028619287338522</v>
+        <v>2.084803351795829</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.600973357877221</v>
+        <v>2.562723749673145</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07874527524248301</v>
+        <v>0.07870504948818588</v>
       </c>
       <c r="C70">
-        <v>5.213323601228547</v>
+        <v>5.059288055558527</v>
       </c>
       <c r="D70">
-        <v>15.04012360122855</v>
+        <v>15.04618805555853</v>
       </c>
       <c r="E70">
-        <v>8.476799999999999</v>
+        <v>8.636899999999999</v>
       </c>
       <c r="F70">
-        <v>10.8868</v>
+        <v>11.0469</v>
       </c>
       <c r="G70">
         <v>1.06</v>
@@ -7140,28 +7140,28 @@
         <v>2.006</v>
       </c>
       <c r="M70">
-        <v>0.78276092</v>
+        <v>0.79427211</v>
       </c>
       <c r="N70">
-        <v>1.22323908</v>
+        <v>1.21172789</v>
       </c>
       <c r="O70">
-        <v>0.3425069424000001</v>
+        <v>0.3392838092000001</v>
       </c>
       <c r="P70">
-        <v>0.8807321376000002</v>
+        <v>0.8724440808</v>
       </c>
       <c r="Q70">
-        <v>1.3647321376</v>
+        <v>1.3564440808</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1360719851327594</v>
+        <v>0.1386617080264061</v>
       </c>
       <c r="T70">
-        <v>2.084803351795829</v>
+        <v>2.144612194605222</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.562723749673145</v>
+        <v>2.525582825764838</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07870504948818588</v>
+        <v>0.08063042373388876</v>
       </c>
       <c r="C71">
-        <v>5.059288055558527</v>
+        <v>4.614298936949421</v>
       </c>
       <c r="D71">
-        <v>15.04618805555853</v>
+        <v>14.76129893694942</v>
       </c>
       <c r="E71">
-        <v>8.636899999999999</v>
+        <v>8.796999999999999</v>
       </c>
       <c r="F71">
-        <v>11.0469</v>
+        <v>11.207</v>
       </c>
       <c r="G71">
         <v>1.06</v>
@@ -7222,45 +7222,45 @@
         <v>2.006</v>
       </c>
       <c r="M71">
-        <v>0.79427211</v>
+        <v>0.8494906</v>
       </c>
       <c r="N71">
-        <v>1.21172789</v>
+        <v>1.1565094</v>
       </c>
       <c r="O71">
-        <v>0.3392838092000001</v>
+        <v>0.3238226320000001</v>
       </c>
       <c r="P71">
-        <v>0.8724440808</v>
+        <v>0.8326867680000001</v>
       </c>
       <c r="Q71">
-        <v>1.3564440808</v>
+        <v>1.316686768</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1386617080264061</v>
+        <v>0.1414240791129625</v>
       </c>
       <c r="T71">
-        <v>2.144612194605222</v>
+        <v>2.208408293601907</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.28</v>
       </c>
       <c r="W71">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.525582825764838</v>
+        <v>2.361415182228032</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08063042373388876</v>
+        <v>0.08061827797959163</v>
       </c>
       <c r="C72">
-        <v>4.614298936949421</v>
+        <v>4.455962273301235</v>
       </c>
       <c r="D72">
-        <v>14.76129893694942</v>
+        <v>14.76306227330124</v>
       </c>
       <c r="E72">
-        <v>8.796999999999999</v>
+        <v>8.957100000000001</v>
       </c>
       <c r="F72">
-        <v>11.207</v>
+        <v>11.3671</v>
       </c>
       <c r="G72">
         <v>1.06</v>
@@ -7304,28 +7304,28 @@
         <v>2.006</v>
       </c>
       <c r="M72">
-        <v>0.8494906</v>
+        <v>0.8616261800000001</v>
       </c>
       <c r="N72">
-        <v>1.1565094</v>
+        <v>1.14437382</v>
       </c>
       <c r="O72">
-        <v>0.3238226320000001</v>
+        <v>0.3204246696000001</v>
       </c>
       <c r="P72">
-        <v>0.8326867680000001</v>
+        <v>0.8239491504000001</v>
       </c>
       <c r="Q72">
-        <v>1.316686768</v>
+        <v>1.3079491504</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1414240791129625</v>
+        <v>0.144376958550316</v>
       </c>
       <c r="T72">
-        <v>2.208408293601907</v>
+        <v>2.27660412356388</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.361415182228032</v>
+        <v>2.328155813464257</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08061827797959163</v>
+        <v>0.0806061322252945</v>
       </c>
       <c r="C73">
-        <v>4.455962273301237</v>
+        <v>4.297626030988136</v>
       </c>
       <c r="D73">
-        <v>14.76306227330124</v>
+        <v>14.76482603098813</v>
       </c>
       <c r="E73">
-        <v>8.957099999999999</v>
+        <v>9.117199999999999</v>
       </c>
       <c r="F73">
-        <v>11.3671</v>
+        <v>11.5272</v>
       </c>
       <c r="G73">
         <v>1.06</v>
@@ -7386,28 +7386,28 @@
         <v>2.006</v>
       </c>
       <c r="M73">
-        <v>0.86162618</v>
+        <v>0.8737617599999999</v>
       </c>
       <c r="N73">
-        <v>1.14437382</v>
+        <v>1.13223824</v>
       </c>
       <c r="O73">
-        <v>0.3204246696000001</v>
+        <v>0.3170267072000001</v>
       </c>
       <c r="P73">
-        <v>0.8239491504000001</v>
+        <v>0.8152115328000002</v>
       </c>
       <c r="Q73">
-        <v>1.3079491504</v>
+        <v>1.2992115328</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.144376958550316</v>
+        <v>0.1475407579474804</v>
       </c>
       <c r="T73">
-        <v>2.276604123563879</v>
+        <v>2.349671084237422</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.328155813464257</v>
+        <v>2.295820316055031</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0806061322252945</v>
+        <v>0.08059398647099739</v>
       </c>
       <c r="C74">
-        <v>4.297626030988136</v>
+        <v>4.139290210161146</v>
       </c>
       <c r="D74">
-        <v>14.76482603098813</v>
+        <v>14.76659021016114</v>
       </c>
       <c r="E74">
-        <v>9.117199999999999</v>
+        <v>9.277299999999999</v>
       </c>
       <c r="F74">
-        <v>11.5272</v>
+        <v>11.6873</v>
       </c>
       <c r="G74">
         <v>1.06</v>
@@ -7468,28 +7468,28 @@
         <v>2.006</v>
       </c>
       <c r="M74">
-        <v>0.8737617599999999</v>
+        <v>0.88589734</v>
       </c>
       <c r="N74">
-        <v>1.13223824</v>
+        <v>1.12010266</v>
       </c>
       <c r="O74">
-        <v>0.3170267072000001</v>
+        <v>0.3136287448000001</v>
       </c>
       <c r="P74">
-        <v>0.8152115328000002</v>
+        <v>0.8064739152</v>
       </c>
       <c r="Q74">
-        <v>1.2992115328</v>
+        <v>1.2904739152</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1475407579474804</v>
+        <v>0.1509389128555458</v>
       </c>
       <c r="T74">
-        <v>2.349671084237422</v>
+        <v>2.428150412368264</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.295820316055031</v>
+        <v>2.264370722684414</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08059398647099739</v>
+        <v>0.08058184071670024</v>
       </c>
       <c r="C75">
-        <v>4.139290210161146</v>
+        <v>3.980954810971379</v>
       </c>
       <c r="D75">
-        <v>14.76659021016114</v>
+        <v>14.76835481097138</v>
       </c>
       <c r="E75">
-        <v>9.277299999999999</v>
+        <v>9.437399999999998</v>
       </c>
       <c r="F75">
-        <v>11.6873</v>
+        <v>11.8474</v>
       </c>
       <c r="G75">
         <v>1.06</v>
@@ -7550,28 +7550,28 @@
         <v>2.006</v>
       </c>
       <c r="M75">
-        <v>0.88589734</v>
+        <v>0.89803292</v>
       </c>
       <c r="N75">
-        <v>1.12010266</v>
+        <v>1.10796708</v>
       </c>
       <c r="O75">
-        <v>0.3136287448000001</v>
+        <v>0.3102307824000001</v>
       </c>
       <c r="P75">
-        <v>0.8064739152</v>
+        <v>0.7977362976000002</v>
       </c>
       <c r="Q75">
-        <v>1.2904739152</v>
+        <v>1.2817362976</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1509389128555458</v>
+        <v>0.154598464295001</v>
       </c>
       <c r="T75">
-        <v>2.428150412368264</v>
+        <v>2.512666611893787</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.264370722684414</v>
+        <v>2.233771118323814</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08058184071670024</v>
+        <v>0.08056969496240313</v>
       </c>
       <c r="C76">
-        <v>3.980954810971379</v>
+        <v>3.822619833569998</v>
       </c>
       <c r="D76">
-        <v>14.76835481097138</v>
+        <v>14.77011983357</v>
       </c>
       <c r="E76">
-        <v>9.437399999999998</v>
+        <v>9.597499999999998</v>
       </c>
       <c r="F76">
-        <v>11.8474</v>
+        <v>12.0075</v>
       </c>
       <c r="G76">
         <v>1.06</v>
@@ -7632,28 +7632,28 @@
         <v>2.006</v>
       </c>
       <c r="M76">
-        <v>0.89803292</v>
+        <v>0.9101684999999999</v>
       </c>
       <c r="N76">
-        <v>1.10796708</v>
+        <v>1.0958315</v>
       </c>
       <c r="O76">
-        <v>0.3102307824000001</v>
+        <v>0.3068328200000001</v>
       </c>
       <c r="P76">
-        <v>0.7977362976000002</v>
+        <v>0.7889986800000002</v>
       </c>
       <c r="Q76">
-        <v>1.2817362976</v>
+        <v>1.27299868</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.154598464295001</v>
+        <v>0.1585507798496125</v>
       </c>
       <c r="T76">
-        <v>2.512666611893787</v>
+        <v>2.603944107381352</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.233771118323814</v>
+        <v>2.20398750341283</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08056969496240313</v>
+        <v>0.08055754920810601</v>
       </c>
       <c r="C77">
-        <v>3.822619833569998</v>
+        <v>3.664285278108256</v>
       </c>
       <c r="D77">
-        <v>14.77011983357</v>
+        <v>14.77188527810825</v>
       </c>
       <c r="E77">
-        <v>9.597499999999998</v>
+        <v>9.757599999999998</v>
       </c>
       <c r="F77">
-        <v>12.0075</v>
+        <v>12.1676</v>
       </c>
       <c r="G77">
         <v>1.06</v>
@@ -7714,28 +7714,28 @@
         <v>2.006</v>
       </c>
       <c r="M77">
-        <v>0.9101684999999999</v>
+        <v>0.92230408</v>
       </c>
       <c r="N77">
-        <v>1.0958315</v>
+        <v>1.08369592</v>
       </c>
       <c r="O77">
-        <v>0.3068328200000001</v>
+        <v>0.3034348576000001</v>
       </c>
       <c r="P77">
-        <v>0.7889986800000002</v>
+        <v>0.7802610624000001</v>
       </c>
       <c r="Q77">
-        <v>1.27299868</v>
+        <v>1.2642610624</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1585507798496125</v>
+        <v>0.162832455033775</v>
       </c>
       <c r="T77">
-        <v>2.603944107381352</v>
+        <v>2.702828060826214</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.20398750341283</v>
+        <v>2.174987667841608</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08055754920810601</v>
+        <v>0.08054540345380888</v>
       </c>
       <c r="C78">
-        <v>3.664285278108256</v>
+        <v>3.505951144737471</v>
       </c>
       <c r="D78">
-        <v>14.77188527810825</v>
+        <v>14.77365114473747</v>
       </c>
       <c r="E78">
-        <v>9.757599999999998</v>
+        <v>9.917699999999998</v>
       </c>
       <c r="F78">
-        <v>12.1676</v>
+        <v>12.3277</v>
       </c>
       <c r="G78">
         <v>1.06</v>
@@ -7796,28 +7796,28 @@
         <v>2.006</v>
       </c>
       <c r="M78">
-        <v>0.92230408</v>
+        <v>0.93443966</v>
       </c>
       <c r="N78">
-        <v>1.08369592</v>
+        <v>1.07156034</v>
       </c>
       <c r="O78">
-        <v>0.3034348576000001</v>
+        <v>0.3000368952000001</v>
       </c>
       <c r="P78">
-        <v>0.7802610624000001</v>
+        <v>0.7715234448000001</v>
       </c>
       <c r="Q78">
-        <v>1.2642610624</v>
+        <v>1.2555234448</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.162832455033775</v>
+        <v>0.167486449799169</v>
       </c>
       <c r="T78">
-        <v>2.702828060826214</v>
+        <v>2.810310618918454</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.174987667841608</v>
+        <v>2.146741074752756</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08054540345380888</v>
+        <v>0.08053325769951175</v>
       </c>
       <c r="C79">
-        <v>3.505951144737471</v>
+        <v>3.347617433609036</v>
       </c>
       <c r="D79">
-        <v>14.77365114473747</v>
+        <v>14.77541743360903</v>
       </c>
       <c r="E79">
-        <v>9.917699999999998</v>
+        <v>10.0778</v>
       </c>
       <c r="F79">
-        <v>12.3277</v>
+        <v>12.4878</v>
       </c>
       <c r="G79">
         <v>1.06</v>
@@ -7878,28 +7878,28 @@
         <v>2.006</v>
       </c>
       <c r="M79">
-        <v>0.93443966</v>
+        <v>0.9465752399999999</v>
       </c>
       <c r="N79">
-        <v>1.07156034</v>
+        <v>1.05942476</v>
       </c>
       <c r="O79">
-        <v>0.3000368952000001</v>
+        <v>0.2966389328000001</v>
       </c>
       <c r="P79">
-        <v>0.7715234448000001</v>
+        <v>0.7627858272000001</v>
       </c>
       <c r="Q79">
-        <v>1.2555234448</v>
+        <v>1.2467858272</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.167486449799169</v>
+        <v>0.1725635349977807</v>
       </c>
       <c r="T79">
-        <v>2.810310618918454</v>
+        <v>2.927564318655444</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.146741074752756</v>
+        <v>2.119218753281567</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08053325769951175</v>
+        <v>0.08052111194521464</v>
       </c>
       <c r="C80">
-        <v>3.347617433609036</v>
+        <v>3.189284144874412</v>
       </c>
       <c r="D80">
-        <v>14.77541743360903</v>
+        <v>14.77718414487441</v>
       </c>
       <c r="E80">
-        <v>10.0778</v>
+        <v>10.2379</v>
       </c>
       <c r="F80">
-        <v>12.4878</v>
+        <v>12.6479</v>
       </c>
       <c r="G80">
         <v>1.06</v>
@@ -7960,28 +7960,28 @@
         <v>2.006</v>
       </c>
       <c r="M80">
-        <v>0.9465752399999999</v>
+        <v>0.95871082</v>
       </c>
       <c r="N80">
-        <v>1.05942476</v>
+        <v>1.04728918</v>
       </c>
       <c r="O80">
-        <v>0.2966389328000001</v>
+        <v>0.2932409704000001</v>
       </c>
       <c r="P80">
-        <v>0.7627858272000001</v>
+        <v>0.7540482096000003</v>
       </c>
       <c r="Q80">
-        <v>1.2467858272</v>
+        <v>1.2380482096</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1725635349977807</v>
+        <v>0.1781241521200697</v>
       </c>
       <c r="T80">
-        <v>2.927564318655444</v>
+        <v>3.055985037415005</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.119218753281567</v>
+        <v>2.09239319944256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08052111194521464</v>
+        <v>0.08050896619091749</v>
       </c>
       <c r="C81">
-        <v>3.189284144874412</v>
+        <v>3.030951278685137</v>
       </c>
       <c r="D81">
-        <v>14.77718414487441</v>
+        <v>14.77895127868514</v>
       </c>
       <c r="E81">
-        <v>10.2379</v>
+        <v>10.398</v>
       </c>
       <c r="F81">
-        <v>12.6479</v>
+        <v>12.808</v>
       </c>
       <c r="G81">
         <v>1.06</v>
@@ -8042,28 +8042,28 @@
         <v>2.006</v>
       </c>
       <c r="M81">
-        <v>0.95871082</v>
+        <v>0.9708464000000001</v>
       </c>
       <c r="N81">
-        <v>1.04728918</v>
+        <v>1.0351536</v>
       </c>
       <c r="O81">
-        <v>0.2932409704000001</v>
+        <v>0.2898430080000001</v>
       </c>
       <c r="P81">
-        <v>0.7540482096000003</v>
+        <v>0.745310592</v>
       </c>
       <c r="Q81">
-        <v>1.2380482096</v>
+        <v>1.229310592</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1781241521200697</v>
+        <v>0.1842408309545875</v>
       </c>
       <c r="T81">
-        <v>3.055985037415005</v>
+        <v>3.197247828050521</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.09239319944256</v>
+        <v>2.066238284449528</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08050896619091749</v>
+        <v>0.08049682043662038</v>
       </c>
       <c r="C82">
-        <v>3.030951278685137</v>
+        <v>2.872618835192817</v>
       </c>
       <c r="D82">
-        <v>14.77895127868514</v>
+        <v>14.78071883519282</v>
       </c>
       <c r="E82">
-        <v>10.398</v>
+        <v>10.5581</v>
       </c>
       <c r="F82">
-        <v>12.808</v>
+        <v>12.9681</v>
       </c>
       <c r="G82">
         <v>1.06</v>
@@ -8124,28 +8124,28 @@
         <v>2.006</v>
       </c>
       <c r="M82">
-        <v>0.9708464000000001</v>
+        <v>0.98298198</v>
       </c>
       <c r="N82">
-        <v>1.0351536</v>
+        <v>1.02301802</v>
       </c>
       <c r="O82">
-        <v>0.2898430080000001</v>
+        <v>0.2864450456000001</v>
       </c>
       <c r="P82">
-        <v>0.745310592</v>
+        <v>0.7365729744000002</v>
       </c>
       <c r="Q82">
-        <v>1.229310592</v>
+        <v>1.2205729744</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1842408309545875</v>
+        <v>0.1910013707190547</v>
       </c>
       <c r="T82">
-        <v>3.197247828050521</v>
+        <v>3.353380386121355</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.066238284449528</v>
+        <v>2.040729169826694</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08049682043662038</v>
+        <v>0.08048467468232326</v>
       </c>
       <c r="C83">
-        <v>2.872618835192817</v>
+        <v>2.714286814549135</v>
       </c>
       <c r="D83">
-        <v>14.78071883519282</v>
+        <v>14.78248681454913</v>
       </c>
       <c r="E83">
-        <v>10.5581</v>
+        <v>10.7182</v>
       </c>
       <c r="F83">
-        <v>12.9681</v>
+        <v>13.1282</v>
       </c>
       <c r="G83">
         <v>1.06</v>
@@ -8206,28 +8206,28 @@
         <v>2.006</v>
       </c>
       <c r="M83">
-        <v>0.98298198</v>
+        <v>0.9951175600000001</v>
       </c>
       <c r="N83">
-        <v>1.02301802</v>
+        <v>1.01088244</v>
       </c>
       <c r="O83">
-        <v>0.2864450456000001</v>
+        <v>0.2830470832</v>
       </c>
       <c r="P83">
-        <v>0.7365729744000002</v>
+        <v>0.7278353568</v>
       </c>
       <c r="Q83">
-        <v>1.2205729744</v>
+        <v>1.2118353568</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1910013707190547</v>
+        <v>0.1985130815684626</v>
       </c>
       <c r="T83">
-        <v>3.353380386121355</v>
+        <v>3.52686100620006</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.040729169826694</v>
+        <v>2.015842228731247</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08048467468232326</v>
+        <v>0.08895844892802612</v>
       </c>
       <c r="C84">
-        <v>2.714286814549135</v>
+        <v>1.415584489853433</v>
       </c>
       <c r="D84">
-        <v>14.78248681454913</v>
+        <v>13.64388448985343</v>
       </c>
       <c r="E84">
-        <v>10.7182</v>
+        <v>10.8783</v>
       </c>
       <c r="F84">
-        <v>13.1282</v>
+        <v>13.2883</v>
       </c>
       <c r="G84">
         <v>1.06</v>
@@ -8288,45 +8288,45 @@
         <v>2.006</v>
       </c>
       <c r="M84">
-        <v>0.9951175600000001</v>
+        <v>1.195947</v>
       </c>
       <c r="N84">
-        <v>1.01088244</v>
+        <v>0.8100530000000004</v>
       </c>
       <c r="O84">
-        <v>0.2830470832</v>
+        <v>0.2268148400000001</v>
       </c>
       <c r="P84">
-        <v>0.7278353568</v>
+        <v>0.5832381600000003</v>
       </c>
       <c r="Q84">
-        <v>1.2118353568</v>
+        <v>1.06723816</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1985130815684626</v>
+        <v>0.2069085231060361</v>
       </c>
       <c r="T84">
-        <v>3.52686100620006</v>
+        <v>3.720751110993906</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.28</v>
       </c>
       <c r="W84">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.015842228731247</v>
+        <v>1.677331855006953</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08895844892802612</v>
+        <v>0.08904854317372901</v>
       </c>
       <c r="C85">
-        <v>1.415584489853433</v>
+        <v>1.244320298944976</v>
       </c>
       <c r="D85">
-        <v>13.64388448985343</v>
+        <v>13.63272029894497</v>
       </c>
       <c r="E85">
-        <v>10.8783</v>
+        <v>11.0384</v>
       </c>
       <c r="F85">
-        <v>13.2883</v>
+        <v>13.4484</v>
       </c>
       <c r="G85">
         <v>1.06</v>
@@ -8370,28 +8370,28 @@
         <v>2.006</v>
       </c>
       <c r="M85">
-        <v>1.195947</v>
+        <v>1.210356</v>
       </c>
       <c r="N85">
-        <v>0.8100530000000004</v>
+        <v>0.7956440000000002</v>
       </c>
       <c r="O85">
-        <v>0.2268148400000001</v>
+        <v>0.2227803200000001</v>
       </c>
       <c r="P85">
-        <v>0.5832381600000003</v>
+        <v>0.5728636800000002</v>
       </c>
       <c r="Q85">
-        <v>1.06723816</v>
+        <v>1.05686368</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2069085231060361</v>
+        <v>0.2163533948358064</v>
       </c>
       <c r="T85">
-        <v>3.720751110993906</v>
+        <v>3.938877478886984</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.677331855006953</v>
+        <v>1.657363618637822</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.089048543173729</v>
+        <v>0.08913863741943187</v>
       </c>
       <c r="C86">
-        <v>1.244320298944979</v>
+        <v>1.073074363432248</v>
       </c>
       <c r="D86">
-        <v>13.63272029894498</v>
+        <v>13.62157436343225</v>
       </c>
       <c r="E86">
-        <v>11.0384</v>
+        <v>11.1985</v>
       </c>
       <c r="F86">
-        <v>13.4484</v>
+        <v>13.6085</v>
       </c>
       <c r="G86">
         <v>1.06</v>
@@ -8452,28 +8452,28 @@
         <v>2.006</v>
       </c>
       <c r="M86">
-        <v>1.210356</v>
+        <v>1.224765</v>
       </c>
       <c r="N86">
-        <v>0.7956440000000005</v>
+        <v>0.7812350000000006</v>
       </c>
       <c r="O86">
-        <v>0.2227803200000001</v>
+        <v>0.2187458000000002</v>
       </c>
       <c r="P86">
-        <v>0.5728636800000003</v>
+        <v>0.5624892000000004</v>
       </c>
       <c r="Q86">
-        <v>1.05686368</v>
+        <v>1.0464892</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2163533948358062</v>
+        <v>0.2270575827962125</v>
       </c>
       <c r="T86">
-        <v>3.938877478886981</v>
+        <v>4.186087362499134</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.657363618637823</v>
+        <v>1.637865223124437</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08913863741943187</v>
+        <v>0.08922873166513476</v>
       </c>
       <c r="C87">
-        <v>1.073074363432248</v>
+        <v>0.9018466385756891</v>
       </c>
       <c r="D87">
-        <v>13.62157436343225</v>
+        <v>13.61044663857569</v>
       </c>
       <c r="E87">
-        <v>11.1985</v>
+        <v>11.3586</v>
       </c>
       <c r="F87">
-        <v>13.6085</v>
+        <v>13.7686</v>
       </c>
       <c r="G87">
         <v>1.06</v>
@@ -8534,28 +8534,28 @@
         <v>2.006</v>
       </c>
       <c r="M87">
-        <v>1.224765</v>
+        <v>1.239174</v>
       </c>
       <c r="N87">
-        <v>0.7812350000000006</v>
+        <v>0.7668260000000005</v>
       </c>
       <c r="O87">
-        <v>0.2187458000000002</v>
+        <v>0.2147112800000001</v>
       </c>
       <c r="P87">
-        <v>0.5624892000000004</v>
+        <v>0.5521147200000003</v>
       </c>
       <c r="Q87">
-        <v>1.0464892</v>
+        <v>1.03611472</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2270575827962125</v>
+        <v>0.2392909404652482</v>
       </c>
       <c r="T87">
-        <v>4.186087362499134</v>
+        <v>4.468612943770168</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.637865223124437</v>
+        <v>1.618820278669501</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08922873166513476</v>
+        <v>0.08931882591083762</v>
       </c>
       <c r="C88">
-        <v>0.9018466385756891</v>
+        <v>0.7306370797818378</v>
       </c>
       <c r="D88">
-        <v>13.61044663857569</v>
+        <v>13.59933707978183</v>
       </c>
       <c r="E88">
-        <v>11.3586</v>
+        <v>11.5187</v>
       </c>
       <c r="F88">
-        <v>13.7686</v>
+        <v>13.9287</v>
       </c>
       <c r="G88">
         <v>1.06</v>
@@ -8616,28 +8616,28 @@
         <v>2.006</v>
       </c>
       <c r="M88">
-        <v>1.239174</v>
+        <v>1.253583</v>
       </c>
       <c r="N88">
-        <v>0.7668260000000005</v>
+        <v>0.7524170000000006</v>
       </c>
       <c r="O88">
-        <v>0.2147112800000001</v>
+        <v>0.2106767600000002</v>
       </c>
       <c r="P88">
-        <v>0.5521147200000003</v>
+        <v>0.5417402400000004</v>
       </c>
       <c r="Q88">
-        <v>1.03611472</v>
+        <v>1.02574024</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2392909404652482</v>
+        <v>0.2534063531602894</v>
       </c>
       <c r="T88">
-        <v>4.468612943770168</v>
+        <v>4.794603999082898</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.618820278669501</v>
+        <v>1.600213149029622</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08931882591083762</v>
+        <v>0.08940892015654051</v>
       </c>
       <c r="C89">
-        <v>0.7306370797818378</v>
+        <v>0.5594456426026948</v>
       </c>
       <c r="D89">
-        <v>13.59933707978183</v>
+        <v>13.58824564260269</v>
       </c>
       <c r="E89">
-        <v>11.5187</v>
+        <v>11.6788</v>
       </c>
       <c r="F89">
-        <v>13.9287</v>
+        <v>14.0888</v>
       </c>
       <c r="G89">
         <v>1.06</v>
@@ -8698,28 +8698,28 @@
         <v>2.006</v>
       </c>
       <c r="M89">
-        <v>1.253583</v>
+        <v>1.267992</v>
       </c>
       <c r="N89">
-        <v>0.7524170000000006</v>
+        <v>0.7380080000000004</v>
       </c>
       <c r="O89">
-        <v>0.2106767600000002</v>
+        <v>0.2066422400000001</v>
       </c>
       <c r="P89">
-        <v>0.5417402400000004</v>
+        <v>0.5313657600000004</v>
       </c>
       <c r="Q89">
-        <v>1.02574024</v>
+        <v>1.01536576</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2534063531602894</v>
+        <v>0.2698743346378375</v>
       </c>
       <c r="T89">
-        <v>4.794603999082898</v>
+        <v>5.17492689694775</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.600213149029622</v>
+        <v>1.58202890869974</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08940892015654051</v>
+        <v>0.08949901440224338</v>
       </c>
       <c r="C90">
-        <v>0.5594456426026948</v>
+        <v>0.3882722827351621</v>
       </c>
       <c r="D90">
-        <v>13.58824564260269</v>
+        <v>13.57717228273516</v>
       </c>
       <c r="E90">
-        <v>11.6788</v>
+        <v>11.8389</v>
       </c>
       <c r="F90">
-        <v>14.0888</v>
+        <v>14.2489</v>
       </c>
       <c r="G90">
         <v>1.06</v>
@@ -8780,28 +8780,28 @@
         <v>2.006</v>
       </c>
       <c r="M90">
-        <v>1.267992</v>
+        <v>1.282401</v>
       </c>
       <c r="N90">
-        <v>0.7380080000000004</v>
+        <v>0.7235990000000003</v>
       </c>
       <c r="O90">
-        <v>0.2066422400000001</v>
+        <v>0.2026077200000001</v>
       </c>
       <c r="P90">
-        <v>0.5313657600000004</v>
+        <v>0.5209912800000003</v>
       </c>
       <c r="Q90">
-        <v>1.01536576</v>
+        <v>1.00499128</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2698743346378375</v>
+        <v>0.2893364945658489</v>
       </c>
       <c r="T90">
-        <v>5.17492689694775</v>
+        <v>5.624399412606212</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.58202890869974</v>
+        <v>1.564253302984012</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08949901440224338</v>
+        <v>0.08958910864794625</v>
       </c>
       <c r="C91">
-        <v>0.3882722827351621</v>
+        <v>0.2171169560204262</v>
       </c>
       <c r="D91">
-        <v>13.57717228273516</v>
+        <v>13.56611695602042</v>
       </c>
       <c r="E91">
-        <v>11.8389</v>
+        <v>11.999</v>
       </c>
       <c r="F91">
-        <v>14.2489</v>
+        <v>14.409</v>
       </c>
       <c r="G91">
         <v>1.06</v>
@@ -8862,28 +8862,28 @@
         <v>2.006</v>
       </c>
       <c r="M91">
-        <v>1.282401</v>
+        <v>1.29681</v>
       </c>
       <c r="N91">
-        <v>0.7235990000000003</v>
+        <v>0.7091900000000004</v>
       </c>
       <c r="O91">
-        <v>0.2026077200000001</v>
+        <v>0.1985732000000001</v>
       </c>
       <c r="P91">
-        <v>0.5209912800000003</v>
+        <v>0.5106168000000003</v>
       </c>
       <c r="Q91">
-        <v>1.00499128</v>
+        <v>0.9946168000000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2893364945658489</v>
+        <v>0.3126910864794626</v>
       </c>
       <c r="T91">
-        <v>5.624399412606212</v>
+        <v>6.163766431396366</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.564253302984012</v>
+        <v>1.546872710728635</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08958910864794625</v>
+        <v>0.08967920289364911</v>
       </c>
       <c r="C92">
-        <v>0.2171169560204262</v>
+        <v>0.04597961844338982</v>
       </c>
       <c r="D92">
-        <v>13.56611695602042</v>
+        <v>13.55507961844339</v>
       </c>
       <c r="E92">
-        <v>11.999</v>
+        <v>12.1591</v>
       </c>
       <c r="F92">
-        <v>14.409</v>
+        <v>14.5691</v>
       </c>
       <c r="G92">
         <v>1.06</v>
@@ -8944,28 +8944,28 @@
         <v>2.006</v>
       </c>
       <c r="M92">
-        <v>1.29681</v>
+        <v>1.311219</v>
       </c>
       <c r="N92">
-        <v>0.7091900000000004</v>
+        <v>0.6947810000000003</v>
       </c>
       <c r="O92">
-        <v>0.1985732000000001</v>
+        <v>0.1945386800000001</v>
       </c>
       <c r="P92">
-        <v>0.5106168000000003</v>
+        <v>0.5002423200000002</v>
       </c>
       <c r="Q92">
-        <v>0.9946168000000003</v>
+        <v>0.9842423200000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3126910864794626</v>
+        <v>0.3412355877072126</v>
       </c>
       <c r="T92">
-        <v>6.163766431396366</v>
+        <v>6.822992787695441</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.546872710728635</v>
+        <v>1.529874109511836</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08967920289364911</v>
+        <v>0.089769297139352</v>
       </c>
       <c r="C93">
-        <v>0.04597961844338982</v>
+        <v>-0.125139773867927</v>
       </c>
       <c r="D93">
-        <v>13.55507961844339</v>
+        <v>13.54406022613207</v>
       </c>
       <c r="E93">
-        <v>12.1591</v>
+        <v>12.3192</v>
       </c>
       <c r="F93">
-        <v>14.5691</v>
+        <v>14.7292</v>
       </c>
       <c r="G93">
         <v>1.06</v>
@@ -9026,28 +9026,28 @@
         <v>2.006</v>
       </c>
       <c r="M93">
-        <v>1.311219</v>
+        <v>1.325628</v>
       </c>
       <c r="N93">
-        <v>0.6947810000000003</v>
+        <v>0.6803720000000004</v>
       </c>
       <c r="O93">
-        <v>0.1945386800000001</v>
+        <v>0.1905041600000001</v>
       </c>
       <c r="P93">
-        <v>0.5002423200000002</v>
+        <v>0.4898678400000003</v>
       </c>
       <c r="Q93">
-        <v>0.9842423200000002</v>
+        <v>0.9738678400000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3412355877072126</v>
+        <v>0.3769162142419002</v>
       </c>
       <c r="T93">
-        <v>6.822992787695441</v>
+        <v>7.647025733069291</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.529874109511836</v>
+        <v>1.513245043104099</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.089769297139352</v>
+        <v>0.1318004006744863</v>
       </c>
       <c r="C94">
-        <v>-0.125139773867927</v>
+        <v>-4.009449856393443</v>
       </c>
       <c r="D94">
-        <v>13.54406022613207</v>
+        <v>9.819850143606555</v>
       </c>
       <c r="E94">
-        <v>12.3192</v>
+        <v>12.4793</v>
       </c>
       <c r="F94">
-        <v>14.7292</v>
+        <v>14.8893</v>
       </c>
       <c r="G94">
         <v>1.06</v>
@@ -9108,45 +9108,45 @@
         <v>2.006</v>
       </c>
       <c r="M94">
-        <v>1.325628</v>
+        <v>2.18574924</v>
       </c>
       <c r="N94">
-        <v>0.6803720000000004</v>
+        <v>-0.1797492399999996</v>
       </c>
       <c r="O94">
-        <v>0.1905041600000001</v>
+        <v>-0.05032978719999989</v>
       </c>
       <c r="P94">
-        <v>0.4898678400000003</v>
+        <v>-0.1294194527999997</v>
       </c>
       <c r="Q94">
-        <v>0.9738678400000003</v>
+        <v>0.3545805472000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3769162142419002</v>
+        <v>0.4337067679115967</v>
       </c>
       <c r="T94">
-        <v>7.647025733069291</v>
+        <v>8.958585864009164</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.28</v>
+        <v>0.2569736682145662</v>
       </c>
       <c r="W94">
-        <v>0.0648</v>
+        <v>0.1090762655061017</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.513245043104099</v>
+        <v>0.9177631007663076</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1318004006744863</v>
+        <v>0.1328104006744863</v>
       </c>
       <c r="C95">
-        <v>-4.009449856393443</v>
+        <v>-4.234008414031324</v>
       </c>
       <c r="D95">
-        <v>9.819850143606555</v>
+        <v>9.755391585968674</v>
       </c>
       <c r="E95">
-        <v>12.4793</v>
+        <v>12.6394</v>
       </c>
       <c r="F95">
-        <v>14.8893</v>
+        <v>15.0494</v>
       </c>
       <c r="G95">
         <v>1.06</v>
@@ -9190,37 +9190,37 @@
         <v>2.006</v>
       </c>
       <c r="M95">
-        <v>2.18574924</v>
+        <v>2.20925192</v>
       </c>
       <c r="N95">
-        <v>-0.1797492399999996</v>
+        <v>-0.2032519199999996</v>
       </c>
       <c r="O95">
-        <v>-0.05032978719999989</v>
+        <v>-0.05691053759999989</v>
       </c>
       <c r="P95">
-        <v>-0.1294194527999997</v>
+        <v>-0.1463413823999997</v>
       </c>
       <c r="Q95">
-        <v>0.3545805472000003</v>
+        <v>0.3376586176000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4337067679115967</v>
+        <v>0.498357895896863</v>
       </c>
       <c r="T95">
-        <v>8.958585864009164</v>
+        <v>10.45168350801069</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2569736682145662</v>
+        <v>0.2542399057867517</v>
       </c>
       <c r="W95">
-        <v>0.1090762655061017</v>
+        <v>0.1094775818305049</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9177631007663076</v>
+        <v>0.9079996635241129</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1328104006744863</v>
+        <v>0.1338204006744863</v>
       </c>
       <c r="C96">
-        <v>-4.234008414031324</v>
+        <v>-4.457726264285744</v>
       </c>
       <c r="D96">
-        <v>9.755391585968674</v>
+        <v>9.691773735714253</v>
       </c>
       <c r="E96">
-        <v>12.6394</v>
+        <v>12.7995</v>
       </c>
       <c r="F96">
-        <v>15.0494</v>
+        <v>15.2095</v>
       </c>
       <c r="G96">
         <v>1.06</v>
@@ -9272,37 +9272,37 @@
         <v>2.006</v>
       </c>
       <c r="M96">
-        <v>2.20925192</v>
+        <v>2.2327546</v>
       </c>
       <c r="N96">
-        <v>-0.2032519199999996</v>
+        <v>-0.2267545999999996</v>
       </c>
       <c r="O96">
-        <v>-0.05691053759999989</v>
+        <v>-0.0634912879999999</v>
       </c>
       <c r="P96">
-        <v>-0.1463413823999997</v>
+        <v>-0.1632633119999997</v>
       </c>
       <c r="Q96">
-        <v>0.3376586176000003</v>
+        <v>0.3207366880000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.498357895896863</v>
+        <v>0.5888694750762358</v>
       </c>
       <c r="T96">
-        <v>10.45168350801069</v>
+        <v>12.54202020961284</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2542399057867517</v>
+        <v>0.2515636962521542</v>
       </c>
       <c r="W96">
-        <v>0.1094775818305049</v>
+        <v>0.1098704493901838</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9079996635241129</v>
+        <v>0.8984417723291223</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1338204006744863</v>
+        <v>0.1348304006744863</v>
       </c>
       <c r="C97">
-        <v>-4.457726264285744</v>
+        <v>-4.680619748111503</v>
       </c>
       <c r="D97">
-        <v>9.691773735714253</v>
+        <v>9.628980251888496</v>
       </c>
       <c r="E97">
-        <v>12.7995</v>
+        <v>12.9596</v>
       </c>
       <c r="F97">
-        <v>15.2095</v>
+        <v>15.3696</v>
       </c>
       <c r="G97">
         <v>1.06</v>
@@ -9354,37 +9354,37 @@
         <v>2.006</v>
       </c>
       <c r="M97">
-        <v>2.2327546</v>
+        <v>2.25625728</v>
       </c>
       <c r="N97">
-        <v>-0.2267545999999996</v>
+        <v>-0.25025728</v>
       </c>
       <c r="O97">
-        <v>-0.0634912879999999</v>
+        <v>-0.07007203840000001</v>
       </c>
       <c r="P97">
-        <v>-0.1632633119999997</v>
+        <v>-0.1801852416</v>
       </c>
       <c r="Q97">
-        <v>0.3207366880000003</v>
+        <v>0.3038147583999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5888694750762358</v>
+        <v>0.7246368438452953</v>
       </c>
       <c r="T97">
-        <v>12.54202020961284</v>
+        <v>15.67752526201606</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2515636962521542</v>
+        <v>0.2489432410828609</v>
       </c>
       <c r="W97">
-        <v>0.1098704493901838</v>
+        <v>0.110255132209036</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8984417723291223</v>
+        <v>0.8890830038673604</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1348304006744863</v>
+        <v>0.1358404006744863</v>
       </c>
       <c r="C98">
-        <v>-4.680619748111502</v>
+        <v>-4.902704785694128</v>
       </c>
       <c r="D98">
-        <v>9.628980251888496</v>
+        <v>9.566995214305869</v>
       </c>
       <c r="E98">
-        <v>12.9596</v>
+        <v>13.1197</v>
       </c>
       <c r="F98">
-        <v>15.3696</v>
+        <v>15.5297</v>
       </c>
       <c r="G98">
         <v>1.06</v>
@@ -9436,37 +9436,37 @@
         <v>2.006</v>
       </c>
       <c r="M98">
-        <v>2.25625728</v>
+        <v>2.27975996</v>
       </c>
       <c r="N98">
-        <v>-0.2502572799999996</v>
+        <v>-0.2737599599999996</v>
       </c>
       <c r="O98">
-        <v>-0.07007203839999988</v>
+        <v>-0.07665278879999989</v>
       </c>
       <c r="P98">
-        <v>-0.1801852415999997</v>
+        <v>-0.1971071711999997</v>
       </c>
       <c r="Q98">
-        <v>0.3038147584000003</v>
+        <v>0.2868928288000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7246368438452933</v>
+        <v>0.9509157917937243</v>
       </c>
       <c r="T98">
-        <v>15.67752526201602</v>
+        <v>20.90336701602135</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2489432410828609</v>
+        <v>0.2463768159170583</v>
       </c>
       <c r="W98">
-        <v>0.110255132209036</v>
+        <v>0.1106318834233758</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8890830038673605</v>
+        <v>0.8799171997037796</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1358404006744863</v>
+        <v>0.1368504006744863</v>
       </c>
       <c r="C99">
-        <v>-4.902704785694128</v>
+        <v>-5.123996889906479</v>
       </c>
       <c r="D99">
-        <v>9.566995214305869</v>
+        <v>9.505803110093519</v>
       </c>
       <c r="E99">
-        <v>13.1197</v>
+        <v>13.2798</v>
       </c>
       <c r="F99">
-        <v>15.5297</v>
+        <v>15.6898</v>
       </c>
       <c r="G99">
         <v>1.06</v>
@@ -9518,37 +9518,37 @@
         <v>2.006</v>
       </c>
       <c r="M99">
-        <v>2.27975996</v>
+        <v>2.30326264</v>
       </c>
       <c r="N99">
-        <v>-0.2737599599999996</v>
+        <v>-0.2972626399999996</v>
       </c>
       <c r="O99">
-        <v>-0.07665278879999989</v>
+        <v>-0.08323353919999989</v>
       </c>
       <c r="P99">
-        <v>-0.1971071711999997</v>
+        <v>-0.2140291007999997</v>
       </c>
       <c r="Q99">
-        <v>0.2868928288000003</v>
+        <v>0.2699708992000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9509157917937243</v>
+        <v>1.403473687690587</v>
       </c>
       <c r="T99">
-        <v>20.90336701602135</v>
+        <v>31.35505052403203</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2463768159170583</v>
+        <v>0.2438627667750475</v>
       </c>
       <c r="W99">
-        <v>0.1106318834233758</v>
+        <v>0.111000945837423</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8799171997037796</v>
+        <v>0.8709384527680266</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1368504006744863</v>
+        <v>0.1378604006744863</v>
       </c>
       <c r="C100">
-        <v>-5.123996889906479</v>
+        <v>-5.344511179252112</v>
       </c>
       <c r="D100">
-        <v>9.505803110093519</v>
+        <v>9.445388820747885</v>
       </c>
       <c r="E100">
-        <v>13.2798</v>
+        <v>13.4399</v>
       </c>
       <c r="F100">
-        <v>15.6898</v>
+        <v>15.8499</v>
       </c>
       <c r="G100">
         <v>1.06</v>
@@ -9600,37 +9600,37 @@
         <v>2.006</v>
       </c>
       <c r="M100">
-        <v>2.30326264</v>
+        <v>2.32676532</v>
       </c>
       <c r="N100">
-        <v>-0.2972626399999996</v>
+        <v>-0.3207653199999996</v>
       </c>
       <c r="O100">
-        <v>-0.08323353919999989</v>
+        <v>-0.08981428959999989</v>
       </c>
       <c r="P100">
-        <v>-0.2140291007999997</v>
+        <v>-0.2309510303999997</v>
       </c>
       <c r="Q100">
-        <v>0.2699708992000003</v>
+        <v>0.2530489696000003</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.403473687690587</v>
+        <v>2.761147375381173</v>
       </c>
       <c r="T100">
-        <v>31.35505052403203</v>
+        <v>62.71010104806406</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2438627667750475</v>
+        <v>0.2413995065045925</v>
       </c>
       <c r="W100">
-        <v>0.111000945837423</v>
+        <v>0.1113625524451258</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8709384527680266</v>
+        <v>0.8621410946592587</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1378604006744863</v>
-      </c>
-      <c r="C101">
-        <v>-5.344511179252112</v>
-      </c>
-      <c r="D101">
-        <v>9.445388820747885</v>
-      </c>
-      <c r="E101">
-        <v>13.4399</v>
-      </c>
-      <c r="F101">
-        <v>15.8499</v>
-      </c>
-      <c r="G101">
-        <v>1.06</v>
-      </c>
-      <c r="H101">
-        <v>13.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.49</v>
-      </c>
-      <c r="K101">
-        <v>0.484</v>
-      </c>
-      <c r="L101">
-        <v>2.006</v>
-      </c>
-      <c r="M101">
-        <v>2.32676532</v>
-      </c>
-      <c r="N101">
-        <v>-0.3207653199999996</v>
-      </c>
-      <c r="O101">
-        <v>-0.08981428959999989</v>
-      </c>
-      <c r="P101">
-        <v>-0.2309510303999997</v>
-      </c>
-      <c r="Q101">
-        <v>0.2530489696000003</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.761147375381173</v>
-      </c>
-      <c r="T101">
-        <v>62.71010104806406</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2413995065045925</v>
-      </c>
-      <c r="W101">
-        <v>0.1113625524451258</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8621410946592587</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
